--- a/模块开发/商品采集汇总.xlsx
+++ b/模块开发/商品采集汇总.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vincentli/PycharmProjects/PythonProject/2026-4 群控/yolo/整合详情页采集/模块开发/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0963116-CD4C-3948-A7BB-7525ED3FE574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFE969B-7E89-924A-8267-938288CBCF74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="520" windowWidth="36760" windowHeight="26540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17720" yWindow="580" windowWidth="32680" windowHeight="26540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="汇总" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3391" uniqueCount="1151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4623" uniqueCount="1519">
   <si>
     <t>序号</t>
   </si>
@@ -3361,119 +3361,1222 @@
     <t>CPB肌肤之钥清爽洁面125ML</t>
   </si>
   <si>
-    <t>25.5</t>
-  </si>
-  <si>
-    <t>279.0</t>
-  </si>
-  <si>
-    <t>205</t>
+    <t>【百补品牌热销40.5万件】Gucci古驰绮梦馥栀女士EDP浓香水100ml 25年新品</t>
+  </si>
+  <si>
+    <t>GUCCI绮梦馥栀100ML</t>
+  </si>
+  <si>
+    <t>2025-09-17</t>
+  </si>
+  <si>
+    <t>【GUCCI】古驰绮梦馥栀香水100ml简装正品持久留香节日礼物自用</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>【正品行货】GUCCI古驰绮梦馥栀女士香水花香调简装无盖EDP 100ml</t>
+  </si>
+  <si>
+    <t>【正品行货】GUCCI古驰花悦绽放慕意香水女士优雅简装EDP 100ml</t>
+  </si>
+  <si>
+    <t>GUCCI花悦绽放100ML浓香</t>
+  </si>
+  <si>
+    <t>【GUCCI】古驰花悦绽放浓香水100ml简装黑盖女士香氛正品持久留香</t>
+  </si>
+  <si>
+    <t>【100ml】古驰 绮梦兰花浓香水EDP简装无盖</t>
+  </si>
+  <si>
+    <t>GUCCI绮梦木兰100ML浓香型</t>
+  </si>
+  <si>
+    <t>2024-05-18</t>
+  </si>
+  <si>
+    <t>GUCCI绮梦栀子花100ML浓香型</t>
+  </si>
+  <si>
+    <t>Gucci古驰 绮梦馥栀女士EDP浓香水100ml 25年新品</t>
+  </si>
+  <si>
+    <t>【GUCCI】古驰绮梦栀子花女士浓香水EDP100ml520节日礼物</t>
+  </si>
+  <si>
+    <t>【正品行货】GUCCI古驰绮梦香草兰浓香水 甜美水生美食调 EDP30ml</t>
+  </si>
+  <si>
+    <t>GUCCI绮梦香草兰香100ml</t>
+  </si>
+  <si>
+    <t>品名相似不足(ratio=25.0%)</t>
+  </si>
+  <si>
+    <t>【正品原装】GUCCI/古驰新品绮梦香草兰浓香EDP香水</t>
+  </si>
+  <si>
+    <t>已选择： 100mL 绮梦香草兰女士香水 1瓶 古驰绮梦香草兰</t>
+  </si>
+  <si>
+    <t>【正品鉴定】GUCCI古驰 2024年新品 绮梦香草兰浓香水/兰花香草</t>
+  </si>
+  <si>
+    <t>已选择： 100mL 古驰 绮梦香草兰 浓香 个人款</t>
+  </si>
+  <si>
+    <t>【原盒正品】GUCCI古驰 2024年新品 绮梦香草兰浓香水/兰花香草</t>
+  </si>
+  <si>
+    <t>【正品行货】GUCCI古驰绮梦香草兰香型女士香水50ml情人节送女友</t>
+  </si>
+  <si>
+    <t>GUCCI绮梦香草兰香50ml</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>【两瓶装】卡诗洗发水黑钻钥源滋养发毛躁润泽保湿护发卡斯洗发水</t>
+  </si>
+  <si>
+    <t>Kerastase卡诗黑钻鱼子酱洗发水250ml</t>
+  </si>
+  <si>
+    <t>已选择： 洗发水250ml  两瓶</t>
+  </si>
+  <si>
+    <t>【HR】赫莲娜绿宝瓶新肌水400ml保湿修护提亮补水精华水</t>
+  </si>
+  <si>
+    <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水400ml</t>
+  </si>
+  <si>
+    <t>【正品行货】HR/赫莲娜绿宝瓶悦活蓄能新肌水400ml</t>
+  </si>
+  <si>
+    <t>2支赫莲娜绿宝瓶新肌水200ml补水保湿</t>
+  </si>
+  <si>
+    <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水200ml</t>
+  </si>
+  <si>
+    <t>已选择： 新肌水200ml*2</t>
+  </si>
+  <si>
+    <t>【赫莲娜】绿宝瓶新肌水200ml/瓶补水保湿</t>
+  </si>
+  <si>
+    <t>【正品行货】HR/赫莲娜绿宝瓶新肌水200ml保湿修护提亮补水精华水</t>
+  </si>
+  <si>
+    <t>【正品行货】SK-II光子小灯泡50ml美白护肤精华液淡斑提亮</t>
+  </si>
+  <si>
+    <t>SK-II光子小灯泡精华露50ml</t>
+  </si>
+  <si>
+    <t>2025-01-17</t>
+  </si>
+  <si>
+    <t>SK-II晶致美肤乳液100g</t>
+  </si>
+  <si>
+    <t>【SK-II】 女士氨基酸清洁洁面乳120g/支</t>
+  </si>
+  <si>
+    <t>SKII女士洗面奶120g/支</t>
+  </si>
+  <si>
+    <t>【正品行货】SKII氨基酸洗面奶护肤洁面乳120g温和控油清洁不刺激</t>
+  </si>
+  <si>
+    <t>【正品行货】SK-II温和护肤洗面奶120g洁面洁净深层清洁控油保湿</t>
+  </si>
+  <si>
+    <t>【SK-II】前男友面膜贴片面膜单片*10组合保湿补水修复抗衰老美白【5天内发货】</t>
+  </si>
+  <si>
+    <t>SK-II前男友面膜10片装</t>
+  </si>
+  <si>
+    <t>【正品行货】SK2前男友面膜10片装焕润嫩肤贴片女友送礼奢护礼盒</t>
+  </si>
+  <si>
+    <t>【SK-II】护肤面膜10片/盒 补水舒缓</t>
+  </si>
+  <si>
+    <t>【正品行货】SKII赋能焕采精华霜大红瓶面霜滋润轻盈保湿紧致养肤</t>
+  </si>
+  <si>
+    <t>SKII大红瓶面霜80g清爽</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>已选择： 大红瓶经典面霜滋润版80g</t>
+  </si>
+  <si>
+    <t>【SK-II】大红瓶面霜80g滋养保湿紧致肌肤清爽款</t>
+  </si>
+  <si>
+    <t>SKII大红瓶面霜80g滋润版保湿紧致肌肤</t>
+  </si>
+  <si>
+    <t>【SK-II】大红瓶面霜80g 滋润版</t>
+  </si>
+  <si>
+    <t>NARS空气唇釉GIPSY吉普赛</t>
+  </si>
+  <si>
+    <t>已选择： 吉普赛GIPSY#684 7.5mL</t>
+  </si>
+  <si>
+    <t>已选择： 684 Gipsy 吉普赛玫瑰 7.5mL 【23年4月产】国际效期5年</t>
+  </si>
+  <si>
+    <t>【特价清仓】NARS纳斯哑光唇釉空气柔雾唇霜#684 Gipsy吉普赛玫瑰</t>
+  </si>
+  <si>
+    <t>【跨境原装】韩国whoo后天气丹华泫花献乳液110ml保湿淡纹正品</t>
+  </si>
+  <si>
+    <t>后Whoo天气丹PRO乳110ML</t>
+  </si>
+  <si>
+    <t>2025-02-18</t>
+  </si>
+  <si>
+    <t>WHOO后天气丹水乳 华泫水150ML乳110ML保湿抗皱</t>
+  </si>
+  <si>
+    <t>韩国thewhoo后黄金气垫粉底液21号#一正两替换自然遮瑕提亮</t>
+  </si>
+  <si>
+    <t>后拱辰享美黄金气垫13G+替换装13G</t>
+  </si>
+  <si>
+    <t>已选择： 后黄金气垫13g*3【21号】</t>
+  </si>
+  <si>
+    <t>【618狂欢购】彩棠面部综合盘4.0眼影修容腮红高光多功能一体化妆</t>
+  </si>
+  <si>
+    <t>TOMFORD幻魅四色眼影盘 #35 玫瑰晶石</t>
+  </si>
+  <si>
+    <t>品牌不一致；规格不匹配；品名相似不足(ratio=22.2%)</t>
+  </si>
+  <si>
+    <t>【正品行货】新版TOM FORD汤姆福特TF四色T壳眼影盘35#新色杏茶盘</t>
+  </si>
+  <si>
+    <t>【正品行货】NARS/娜斯四色眼影盘掌心盘圣保罗绝美温柔清透</t>
+  </si>
+  <si>
+    <t>品牌不一致；规格不匹配</t>
+  </si>
+  <si>
+    <t>SK-II小灯泡新版50ml</t>
+  </si>
+  <si>
+    <t>SK-II/sk2/光蕴恒璨焕亮精华露新版光子小灯泡祛斑美白50ml正品</t>
+  </si>
+  <si>
+    <t>SKII光子小灯泡75ml</t>
+  </si>
+  <si>
+    <t>已选择： 新版光子小灯泡75ml【正品保证】</t>
+  </si>
+  <si>
+    <t>SKII洁面油250ml</t>
+  </si>
+  <si>
+    <t>【正品行货】SKII男士焕活保湿洁面洗面奶120g深层洁净控油清爽</t>
+  </si>
+  <si>
+    <t>【SK-II】护肤洁面油卸妆油250ml 卸妆洁面二合一深层清洁温和洁净【5天内发货】</t>
+  </si>
+  <si>
+    <t>【SK-II】护肤洁面油250ml卸妆油温和洁净深层清洁控油【5天内发货】</t>
+  </si>
+  <si>
+    <t>正品SK-II护肤洁面油卸妆油250ml卸妆洁面二合一深层清洁温和洁净【5天内发货】</t>
+  </si>
+  <si>
+    <t>【Givenchy】纪梵希高定丝绒唇釉 N51 N15  N36 N37</t>
+  </si>
+  <si>
+    <t>纪梵希粉丝绒N37</t>
+  </si>
+  <si>
+    <t>2023-06-01</t>
+  </si>
+  <si>
+    <t>已选择： 复古丝绒 N37 6.5mL</t>
+  </si>
+  <si>
+    <t>【正品行货】YSL圣罗兰全新爱心唇釉610 416 622 440限定浮雕黑管</t>
+  </si>
+  <si>
+    <t>圣罗兰爱心黑管唇釉440</t>
+  </si>
+  <si>
+    <t>【正品行货】YSL圣罗兰全新爱心唇釉440 610 416 622限定浮雕黑管</t>
+  </si>
+  <si>
+    <t>已选择： 440 野玫瑰 5.5mL</t>
+  </si>
+  <si>
+    <t>【正品行货】YSL/圣罗兰全新黑管唇釉440爱心限量版</t>
+  </si>
+  <si>
+    <t>两支 单品 雅诗兰黛新款红石榴洗面奶125ml</t>
+  </si>
+  <si>
+    <t>雅诗兰黛红石榴洁面125ml两支装</t>
+  </si>
+  <si>
+    <t>【雅诗兰黛】新款红石榴滋润精华水200ml保湿补水</t>
+  </si>
+  <si>
+    <t>雅诗兰黛红石榴水200ml两支装</t>
+  </si>
+  <si>
+    <t>SK2小银瓶50ml两瓶装</t>
+  </si>
+  <si>
+    <t>SK2大红瓶滋润面霜50g</t>
+  </si>
+  <si>
+    <t>【520礼物】SK-II大红瓶面霜50g限定礼盒紧致上扬保湿润提亮紧致</t>
+  </si>
+  <si>
+    <t>【Fresh】馥蕾诗西柚/睡莲/小苍兰香皂250g 深层清洁香皂</t>
+  </si>
+  <si>
+    <t>馥蕾诗西柚香皂</t>
+  </si>
+  <si>
+    <t>【Fresh】馥蕾诗西柚香皂250g 深层清洁香皂</t>
+  </si>
+  <si>
+    <t>【42.1万人收藏该品牌】FRESH/馥蕾诗玫瑰花瓣水250ml*2瓶</t>
+  </si>
+  <si>
+    <t>馥蕾诗玫瑰花瓣水400ml</t>
+  </si>
+  <si>
+    <t>超粘超软 JNM GL70Ultra 升级款羽毛球拍手胶吸汗防滑减震</t>
+  </si>
+  <si>
+    <t>【馥蕾诗】 大马士革玫瑰花瓣润泽密集保湿爽肤水400ml高保湿深层滋润【5天内发货】</t>
+  </si>
+  <si>
+    <t>【Fresh】馥蕾诗玫瑰花瓣水250ml大马士革玫瑰润泽保湿爽肤水调理肌肤【5天内发货】</t>
+  </si>
+  <si>
+    <t>【正品行货】馥蕾诗红茶凝时焕活面霜50ml淡纹紧致增加光泽</t>
+  </si>
+  <si>
+    <t>馥蕾诗红茶紧致面霜50ml</t>
+  </si>
+  <si>
+    <t>【Fresh】馥蕾诗青春赋活面霜日霜紧致肌肤抗皱提亮深度保湿香港仓发【5天内发货】</t>
+  </si>
+  <si>
+    <t>馥蕾诗睡莲日霜50ml</t>
+  </si>
+  <si>
+    <t>【Fresh】馥蕾诗睡莲青春赋活面霜Lotus面霜保湿滋养修护提亮肤色50ml【5天内发货】</t>
+  </si>
+  <si>
+    <t>【Fresh】馥蕾诗玫瑰保湿面霜50ml  密集保湿舒缓补水</t>
+  </si>
+  <si>
+    <t>馥蕾诗玫瑰保湿面霜50ml两瓶装</t>
+  </si>
+  <si>
+    <t>2025-12-02</t>
+  </si>
+  <si>
+    <t>【Fresh】馥蕾诗小苍兰香皂250g 深层清洁香皂</t>
+  </si>
+  <si>
+    <t>馥蕾诗小苍兰香皂</t>
+  </si>
+  <si>
+    <t>【正品行货】雅诗兰黛白金级养肤粉底液宝石粉底光感保湿透亮遮瑕</t>
+  </si>
+  <si>
+    <t>雅诗兰黛白金粉底液1W0</t>
+  </si>
+  <si>
+    <t>【专柜行货】雅诗兰黛白金养肤粉底液 持久遮瑕保湿抗氧化服帖</t>
+  </si>
+  <si>
+    <t>【Fresh】馥蕾诗酵母酵萃红茶水250ml保湿补水清爽滋润爽肤水精华水</t>
+  </si>
+  <si>
+    <t>馥蕾诗红茶精粹水250ml</t>
+  </si>
+  <si>
+    <t>【雅诗兰黛】白金粉底液1C0养肤透亮持久保湿遮瑕服帖【5天内发货】</t>
+  </si>
+  <si>
+    <t>雅诗兰黛白金粉底液1CO</t>
+  </si>
+  <si>
+    <t>2024-11-05</t>
+  </si>
+  <si>
+    <t>【正品行货】娇韵诗牛奶水减黄提亮美白淡斑清爽200ml保湿细腻</t>
+  </si>
+  <si>
+    <t>娇韵诗美白滋润水200ml</t>
+  </si>
+  <si>
+    <t>CLARINS/娇韵诗焕颜紧致弹簧霜晚霜 50ml修护提亮 娇韵诗弹簧晚霜【5天内发货】</t>
+  </si>
+  <si>
+    <t>娇韵诗焕颜紧致晚霜50ml</t>
+  </si>
+  <si>
+    <t>【Clarins】娇韵诗焕颜弹力元气晚霜滋润型50ml紧致回弹保湿淡纹面霜【5天内发货】</t>
+  </si>
+  <si>
+    <t>【正品】娇韵诗焕颜紧致弹簧晚霜淡纹胶原回弹滋润抗皱面霜女50ml</t>
+  </si>
+  <si>
+    <t>Clarins/娇韵诗焕颜弹力元气晚霜滋润型50ml紧致回弹保湿淡纹面霜【5天内发货】</t>
+  </si>
+  <si>
+    <t>Clarins娇韵诗焕颜紧致晚霜50ml</t>
+  </si>
+  <si>
+    <t>【Clarins】娇韵诗焕颜弹力晚霜面霜50ml保湿提拉紧致滋润【5天内发货】</t>
+  </si>
+  <si>
+    <t>【雅诗兰黛】多效智妍面霜(清爽版)75ml双支</t>
+  </si>
+  <si>
+    <t>雅诗兰黛多效智妍乳霜75ml清爽</t>
+  </si>
+  <si>
+    <t>【梅森马吉拉】慵懒周末身体乳200ml润肤乳保湿补水</t>
+  </si>
+  <si>
+    <t>马丁马吉拉慵懒周末身体乳200ml</t>
+  </si>
+  <si>
+    <t>【正品行货】兰蔻新款持妆粉底液30ml PO-01</t>
+  </si>
+  <si>
+    <t>兰蔻养肤水粉底液 PO-01 30ml</t>
+  </si>
+  <si>
+    <t>【Kiehl's】科颜氏男士保湿乳液125ml活力清爽控油补水收缩毛孔送男友</t>
+  </si>
+  <si>
+    <t>科颜氏男士乳液125ml</t>
+  </si>
+  <si>
+    <t>【科颜氏】男士保湿乳液125ml补水保湿清爽改善暗沉</t>
+  </si>
+  <si>
+    <t>【科颜氏】男士保湿乳液125ml补水保湿清爽改善暗沉礼物</t>
+  </si>
+  <si>
+    <t>【品牌好评322.1万+条】Kiehl's/科颜氏男士活力保湿乳液125ml补水保湿润肤改善干燥</t>
+  </si>
+  <si>
+    <t>科颜氏果冻清爽高保湿霜50ml/瓶</t>
+  </si>
+  <si>
+    <t>【娇韵诗】双萃焕活修护精华露100ml清爽九代补水</t>
+  </si>
+  <si>
+    <t>娇韵诗第九代全新双萃焕活修护精华 100ML</t>
+  </si>
+  <si>
+    <t>【跨境原装】安耐晒防晒霜安热沙隔离小金瓶90ml防水防汗资生堂女</t>
+  </si>
+  <si>
+    <t>资生堂安耐晒90ml</t>
+  </si>
+  <si>
+    <t>2025-06-22</t>
+  </si>
+  <si>
+    <t>【跨境原装】资生堂安耐晒防晒霜清爽不油面部防紫外线敏感肌正品</t>
+  </si>
+  <si>
+    <t>2025-05-31</t>
+  </si>
+  <si>
+    <t>已选: 软管90ml [盒装版]防晒霜+绵羊乳霜6g</t>
+  </si>
+  <si>
+    <t>【保税原装】资生堂安耐晒防晒霜安热沙防晒霜小金瓶防水防汗隔离</t>
+  </si>
+  <si>
+    <t>2025-08-16</t>
+  </si>
+  <si>
+    <t>规格不匹配；规格匹配失败</t>
+  </si>
+  <si>
+    <t>匹配失败</t>
+  </si>
+  <si>
+    <t>【保税原装】资生堂安耐晒防晒霜紫外线防水防汗防晒乳隔离霜正品</t>
+  </si>
+  <si>
+    <t>2025-06-06</t>
+  </si>
+  <si>
+    <t>已选: [原装保税]防晒霜90ml+面霜乳6g</t>
+  </si>
+  <si>
+    <t>安热沙Anessa安耐晒防晒霜面部防晒男女军训防晒清爽防晒小金软管【6月18日发完】</t>
+  </si>
+  <si>
+    <t>安耐晒金钻高效防晒90ml</t>
+  </si>
+  <si>
+    <t>【保税原装】安耐晒安热沙防晒霜90ml水润清爽防水防汗户外小金瓶</t>
+  </si>
+  <si>
+    <t>2026-01-03</t>
+  </si>
+  <si>
+    <t>【20.9万人回购该品牌】ANESSA/安热沙/安耐晒小金瓶防晒霜60ML</t>
+  </si>
+  <si>
+    <t>雅诗兰黛樱花微精华原生液400ml 肌肤赋活保湿滋润提亮修护爽肤水【12天内发货】</t>
+  </si>
+  <si>
+    <t>雅诗兰黛樱花微精华原生液400ml</t>
+  </si>
+  <si>
+    <t>【雅诗兰黛】樱花微精华原生液400ml肌肤赋活保湿滋润提亮修护爽肤水【5天内发货】</t>
+  </si>
+  <si>
+    <t>【雅诗兰黛】樱花水微精华原生液补水保湿提亮肤色收缩毛孔湿敷精华水</t>
+  </si>
+  <si>
+    <t>2024-11-15</t>
+  </si>
+  <si>
+    <t>【正品行货】YSL/圣罗兰口红小金条21复古红小黑条大牌杨树林哑光</t>
+  </si>
+  <si>
+    <t>圣罗兰小金条细管口红21号复古正红色</t>
+  </si>
+  <si>
+    <t>【正品行货】YSL/圣罗兰口红小金条 21复古红显白大牌正品礼盒装</t>
+  </si>
+  <si>
+    <t>芭比布朗清润舒盈新版卸妆油200ml/瓶 温和卸妆</t>
+  </si>
+  <si>
+    <t>芭比布朗舒缓卸妆洁面油200ml</t>
+  </si>
+  <si>
+    <t>芭比布朗清润舒盈新版卸妆油200ml 温和卸妆</t>
+  </si>
+  <si>
+    <t>两瓶 单品 芭比布朗清透舒盈卸妆油200ml/瓶</t>
+  </si>
+  <si>
+    <t>【海外直采】顺丰Clarins娇韵诗第九代双萃赋活精华露100ml</t>
+  </si>
+  <si>
+    <t>娇韵诗双萃焕活修护精华露100ml</t>
+  </si>
+  <si>
+    <t>2024-07-08</t>
+  </si>
+  <si>
+    <t>【阿玛尼】权利红黑管唇膏410瞩目绯红3.1g 显白提气色口红【26年8月</t>
+  </si>
+  <si>
+    <t>阿玛尼权力口红410色</t>
+  </si>
+  <si>
+    <t>【正品行货】YSL圣罗兰黑金浮雕方管大牌口红R1966杨树林唇膏正品</t>
+  </si>
+  <si>
+    <t>YSL圣罗兰黑金方管13色</t>
+  </si>
+  <si>
+    <t>【正品行货】YSL圣罗兰黑金方管口红 釉光新品10/06/11 裸色温柔</t>
+  </si>
+  <si>
+    <t>2023-12-30</t>
+  </si>
+  <si>
+    <t>已选择： 推荐#13-偏执</t>
+  </si>
+  <si>
+    <t>【正品行货】ysl/圣罗兰大牌口红nm裸缪斯黑金浮雕方管大牌礼盒装</t>
+  </si>
+  <si>
+    <t>YSL圣罗兰黑金方管14色</t>
+  </si>
+  <si>
+    <t>14:35</t>
+  </si>
+  <si>
+    <t>品牌不一致；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+  </si>
+  <si>
+    <t>【正品行货】YSL圣罗兰全新黑金方管口红 缎光质地显白</t>
+  </si>
+  <si>
+    <t>【正品行货】圣罗兰/YSL方管口红黑金浮雕NM裸缪斯大牌正品礼盒装</t>
+  </si>
+  <si>
+    <t>YSL圣罗兰黑金方管1968</t>
+  </si>
+  <si>
+    <t>【正品行货】YSL/圣罗兰全新黑管唇釉610 416 442 443爱心限量版</t>
+  </si>
+  <si>
+    <t>【正品行货】YSL圣罗兰口红1966小金条314小黑条杨树林大牌正品</t>
+  </si>
+  <si>
+    <t>2025-03-20</t>
+  </si>
+  <si>
+    <t>规格不匹配；品名相似不足(ratio=25.0%)；规格匹配失败</t>
+  </si>
+  <si>
+    <t>品牌不一致；规格不匹配；规格匹配失败</t>
+  </si>
+  <si>
+    <t>YSL/圣罗兰黑金浮雕方管釉光滋润质感唇膏口红06偏见高定礼盒包装</t>
+  </si>
+  <si>
+    <t>【YSL】圣罗兰黑金浮雕方管唇膏口红1968透视1971 14 11礼盒装520礼物</t>
+  </si>
+  <si>
+    <t>规格匹配失败</t>
+  </si>
+  <si>
+    <t>YSL/圣罗兰黑金浮雕方管釉光唇膏口红1971流言06裸缪斯NM1968正品</t>
+  </si>
+  <si>
+    <t>【YSL】圣罗兰啵啵丰盈唇冻光耀丰盈唇釉银盖日常通勤提升气色6ml【5天内发货】</t>
+  </si>
+  <si>
+    <t>YSL圣罗兰银管02色</t>
+  </si>
+  <si>
+    <t>已选择： YSL啵啵唇冻#02 霜冻粉色 6mL</t>
+  </si>
+  <si>
+    <t>【Clinique】倩碧黄油滋润(有油)125ml</t>
+  </si>
+  <si>
+    <t>倩碧有油润肤乳125ml</t>
+  </si>
+  <si>
+    <t>【正品行货】Clinique/倩碧黄油无油有油乳液保湿滋润滋养</t>
+  </si>
+  <si>
+    <t>已选择： 倩碧黄油125ml无油</t>
+  </si>
+  <si>
+    <t>【正品行货】Clinique/倩碧黄油无油有油乳液保湿滋润滋养125ml*2</t>
+  </si>
+  <si>
+    <t>LA MER/海蓝之谜臻璨焕活精华油30ml抗老淡纹</t>
+  </si>
+  <si>
+    <t>海蓝之谜 臻璨焕活精华油30ml （万能油）</t>
+  </si>
+  <si>
+    <t>2025-07-02</t>
+  </si>
+  <si>
+    <t>SK2大红瓶清爽版80g</t>
+  </si>
+  <si>
+    <t>SK2大红瓶滋润版80g</t>
+  </si>
+  <si>
+    <t>雅诗兰黛ESTEE LAUDER新版红石榴能量水清爽型 200ML</t>
+  </si>
+  <si>
+    <t>SK-II 小银瓶精华50ML</t>
+  </si>
+  <si>
+    <t>阿玛尼大师粉底液2号</t>
+  </si>
+  <si>
+    <t>【Lancome】 兰蔻 美丽人生女士香水EDP 30/100ML</t>
+  </si>
+  <si>
+    <t>Lancome兰蔻美丽人生馥郁版100ml</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>【专柜行货】兰蔻新品美丽人生香水50ml 浓香版EDP 女士香水</t>
+  </si>
+  <si>
+    <t>Lancome兰蔻美丽人生馥郁版50ml</t>
+  </si>
+  <si>
+    <t>【Lancome】兰蔻美丽人生馥郁版女士浓香香水EDP 30-100ml【5天内发货】</t>
+  </si>
+  <si>
+    <t>已选择： 50ml</t>
+  </si>
+  <si>
+    <t>【Lancome】兰蔻美丽人生馥郁版女士浓香EDP 30-50-100ml【法国直发】【5天内发货】</t>
+  </si>
+  <si>
+    <t>【Lancome】兰蔻美丽人生馥郁版女浓香EDP 30-100ml【法国直发【5天内发货】</t>
+  </si>
+  <si>
+    <t>兰蔻 美丽人生香氛精华香水 50ml</t>
+  </si>
+  <si>
+    <t>已选择： 50mL</t>
+  </si>
+  <si>
+    <t>LANCOME兰蔻美丽人生女士淡香精EDP30/50/100ML精装</t>
+  </si>
+  <si>
+    <t>【Lancome】兰蔻 美丽人生女士浓香水 30/50/100ml【法国直发】【5天内发货】</t>
+  </si>
+  <si>
+    <t>Lancome/兰蔻是我IDOLE偶像香水 50ml</t>
+  </si>
+  <si>
+    <t>【兰蔻】唯我浓香水100ml花果香调清新持久馥郁迷人节日礼物</t>
+  </si>
+  <si>
+    <t>Lancome 兰蔻是我 浓情版 100ml</t>
+  </si>
+  <si>
+    <t>【兰蔻】是我偶像经典浓香水EDP100ML补充装花香调新版</t>
+  </si>
+  <si>
+    <t>古驰(GUCCI)绮梦茉莉女士香水EDP 30/50/100ML</t>
+  </si>
+  <si>
+    <t>GUCCI 香水 茉莉100ML</t>
+  </si>
+  <si>
+    <t>2024-11-07</t>
+  </si>
+  <si>
+    <t>【Hermes】爱马仕李先生的花园淡香水EDT100ml</t>
+  </si>
+  <si>
+    <t>爱马仕李先生的花园淡香水100ml</t>
+  </si>
+  <si>
+    <t>【Hermes】爱马仕绯红火参/血色大黄古龙水香水节日礼物</t>
+  </si>
+  <si>
+    <t>爱马仕绯红火参古龙水100ml</t>
+  </si>
+  <si>
+    <t>已选择： 100mL 血色大黄 EDC 古龙水</t>
+  </si>
+  <si>
+    <t>【Hermes】爱马仕绯红火参/血色大黄古龙水香水简装礼物</t>
+  </si>
+  <si>
+    <t>已选择： 100mL 血色大黄 EDC 古龙水【简装】</t>
+  </si>
+  <si>
+    <t>纳斯小粉金口红321TURNED ON#透茶玫瑰1.5g节日礼物</t>
+  </si>
+  <si>
+    <t>NARS小粉金细管唇膏1.5G #321 Turned on</t>
+  </si>
+  <si>
+    <t>已选择： 1.5g #321 Turned On 透茶玫瑰</t>
+  </si>
+  <si>
+    <t>【NARS】氛围娜斯小粉唇膏#321透茶玫瑰丝滑显色保湿滋润水感通透1.5g</t>
+  </si>
+  <si>
+    <t>MAC/魅可大子弹头口红唇膏#646   3.5g</t>
+  </si>
+  <si>
+    <t>MAC 丝柔哑光唇膏 #646 MARRAKESH 肉桂红茶</t>
+  </si>
+  <si>
+    <t>品名相似不足(ratio=11.8%)</t>
+  </si>
+  <si>
+    <t>【正品行货】MAC/魅可大子弹头口红 662大辣椒唇膏 显色哑光滋润</t>
+  </si>
+  <si>
+    <t>规格不匹配；品名相似不足(ratio=11.8%)</t>
+  </si>
+  <si>
+    <t>已选择： #646*大女主+专柜礼盒 正品行货-送礼好物-可代写祝福贺卡</t>
+  </si>
+  <si>
+    <t>【MAC】魅可新品哑光大子弹头唇膏口红666大宠粉 683大玩咖 682 646【5天内发货】</t>
+  </si>
+  <si>
+    <t>品名相似不足(ratio=29.4%)</t>
+  </si>
+  <si>
+    <t>已选择： #646MARRAKESH 大女主</t>
+  </si>
+  <si>
+    <t>【鉴定正品】MAC/魅可新经典哑光唇膏 柔雾 气色 3.5g 大子弹头</t>
+  </si>
+  <si>
+    <t>规格不匹配；品名相似不足(ratio=23.5%)</t>
+  </si>
+  <si>
+    <t>已选择：#646 3.5g MAC 经典大子弹头</t>
+  </si>
+  <si>
+    <t>【正品行货】Lamer海蓝之谜修护焕新精萃水100ml 修护舒缓精华水</t>
+  </si>
+  <si>
+    <t>LAMER海蓝之谜调理焕肤液100ml</t>
+  </si>
+  <si>
+    <t>【LA MER】 海蓝之谜焕肤水100ML 舒缓提亮滋润【5天内发货】</t>
+  </si>
+  <si>
+    <t>【海蓝之谜】精粹柔酸水肌底液精华换肤调理液100ml 控油保湿改善闭口【5天内发货】</t>
+  </si>
+  <si>
+    <t>【LA MER】海蓝之谜鞣酸水柔酸肌底液100ml复合精华细致毛孔调理焕肤【5天内发货】</t>
+  </si>
+  <si>
+    <t>【MAC】魅可定妆保湿喷雾白瓶100ml补水控油持久干皮油皮滋养清爽正品</t>
+  </si>
+  <si>
+    <t>MAC魅可保湿定妆喷雾Fix+100mL</t>
+  </si>
+  <si>
+    <t>MAC妆前瞬间定妆喷雾100ML</t>
+  </si>
+  <si>
+    <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+  </si>
+  <si>
+    <t>【MAC】魅可定妆紫喷喷雾持久锁妆防水保湿控油不拔干不刺激干皮100ml【5天内发货】</t>
+  </si>
+  <si>
+    <t>MAC/魅可定妆妆前保湿喷雾原味长效定妆防水不黏腻</t>
+  </si>
+  <si>
+    <t>已选: 100mL 妆前保湿喷雾[24.1产]</t>
+  </si>
+  <si>
+    <t>【MAC】魅可 新升级定制无瑕粉底液NC12#30ml</t>
+  </si>
+  <si>
+    <t>MAC 无暇粉底液NC12 30ML</t>
+  </si>
+  <si>
+    <t>已选: NC12 黄二白</t>
+  </si>
+  <si>
+    <t>雅诗兰黛 红石榴面霜50ml</t>
+  </si>
+  <si>
+    <t>雅诗兰黛 红石榴洁面125ml</t>
+  </si>
+  <si>
+    <t>【861.8万人收藏该品牌】双支 单品 雅诗兰黛新款红石榴洗面奶125ml</t>
+  </si>
+  <si>
+    <t>【跨境原装】资生堂红腰子洗面奶女洁面乳膏氨基酸清洁保湿旗舰店</t>
+  </si>
+  <si>
+    <t>资生堂/SHISEIDO红腰子洁面125ml</t>
+  </si>
+  <si>
+    <t>2025-08-12</t>
+  </si>
+  <si>
+    <t>已选: 125ml [温和保湿]红腰子洁面乳+嫩白洇色蛋</t>
+  </si>
+  <si>
+    <t>【跨境原装】资生堂洁面膏红腰子洗面奶深层清洁保湿去黄黑头提亮</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>已选: 175ml[正装125ml+中样50ml]洁面膏+滴形妆蛋球1</t>
+  </si>
+  <si>
+    <t>【特价清仓】资生堂悦薇智感紧塑焕白眼霜15ml 紧致淡纹提亮眼周</t>
+  </si>
+  <si>
+    <t>资生堂/SHISEIDO悦薇抗糖眼霜（新版）15ml</t>
+  </si>
+  <si>
+    <t>【正品行货】资生堂盼丽风姿智感抚纹眼霜15ml小雷达抗皱紧致礼物</t>
+  </si>
+  <si>
+    <t>资生堂/SHISEIDO盼丽风姿眼霜（新款）15ml</t>
+  </si>
+  <si>
+    <t>【雅诗兰黛】DW持妆粉底液1C1 66#瓷白色 30ml</t>
+  </si>
+  <si>
+    <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1C1 30ML 新版 2026年</t>
+  </si>
+  <si>
+    <t>Estee Lauder/雅诗兰黛 DW持妆粉底液30ml#1N2 柔光遮瑕【5天内发货】</t>
+  </si>
+  <si>
+    <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1N2 30ML 新版 2026</t>
+  </si>
+  <si>
+    <t>Estee Lauder/雅诗兰黛dw持粉底液#1N2油皮亲妈持妆粉底液30ml【5天内发货】</t>
+  </si>
+  <si>
+    <t>【原装正品】雅诗兰黛DW持妆粉底液 油皮亲妈持久不脱妆遮瑕控油</t>
+  </si>
+  <si>
+    <t>已选: 1W2 自然色（全新原装） 30mL 个人 DW-粉底液 赠彩妆蛋 压头[新旧版随机]</t>
+  </si>
+  <si>
+    <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1N1 30ML 新版 2026</t>
+  </si>
+  <si>
+    <t>已选: 30mL 1N2</t>
+  </si>
+  <si>
+    <t>【正品行货】MAC/魅可大子弹头口红哑光柔雾666大宠粉602大辣椒</t>
+  </si>
+  <si>
+    <t>MAC魅可 丝柔哑光唇膏 大子弹口红#666 Sweet Deal 玫瑰冷萃</t>
+  </si>
+  <si>
+    <t>已选: 大宠粉[666] 赠专柜礼盒+正品保障+假一赔十</t>
+  </si>
+  <si>
+    <t>【累计热销401万+件】韩国兰芝新款马卡龙防晒隔离霜30ml遮瑕妆前乳打底</t>
+  </si>
+  <si>
+    <t>兰芝马卡龙隔离30ml紫色</t>
+  </si>
+  <si>
+    <t>2025-03-26</t>
+  </si>
+  <si>
+    <t>【累计热销401万+件】韩国LANEIGE兰芝新款马卡龙防晒隔离霜遮瑕三合一妆前乳打底</t>
+  </si>
+  <si>
+    <t>兰芝马卡龙隔离30ml绿色</t>
+  </si>
+  <si>
+    <t>2025-03-24</t>
+  </si>
+  <si>
+    <t>已选: 兰芝紫隔离30ml[新版马卡龙]</t>
+  </si>
+  <si>
+    <t>【资生堂】悦薇抗糖面霜智感塑颜抗皱霜焕白清爽资生堂面霜50ml【5天内发货】</t>
+  </si>
+  <si>
+    <t>资生堂 悦薇大抗糖滋润面霜（新款）50mL</t>
+  </si>
+  <si>
+    <t>【资生堂】悦薇面霜抗糖抗初老补水紧致智感紧塑焕白霜</t>
+  </si>
+  <si>
+    <t>已选: 50mL [滋润型]悦薇面霜</t>
+  </si>
+  <si>
+    <t>【NARS】娜斯5894大白饼粉饼控油磨皮持妆蜜粉饼【5天内发货】</t>
+  </si>
+  <si>
+    <t>NARS蜜粉饼5894 效期24年</t>
+  </si>
+  <si>
+    <t>【NARS】娜斯 流光美肌轻透蜜粉饼5894大白饼粉饼10g【5天内发货】</t>
+  </si>
+  <si>
+    <t>2024-08-27</t>
+  </si>
+  <si>
+    <t>【累计热销248.5万+件】whoo后拱辰享泡沫洗面奶水妍津率享深层清洁控油洁面女</t>
+  </si>
+  <si>
+    <t>WHOO/后拱辰享洁面泡沫180ml/支 （新条码）</t>
+  </si>
+  <si>
+    <t>已选: 美白洁面套180ML+洁面40ML</t>
+  </si>
+  <si>
+    <t>【资生堂】红腰子精华液4.0紧致抗皱面部护肤抗初老120ml</t>
+  </si>
+  <si>
+    <t>SHISEIDO资生堂红腰子精华100ml</t>
+  </si>
+  <si>
+    <t>【1.37万人评价品牌正品】GUCCI/古驰炼金士花园系列香水100ML正品香氛送礼</t>
+  </si>
+  <si>
+    <t>古驰炼金师花园香草颂香水100ML</t>
+  </si>
+  <si>
+    <t>【百补品牌热销40.6万件】GUCCI/古驰炼金士花园系列香水150ML简装持久留香</t>
+  </si>
+  <si>
+    <t>古驰炼金师花园沐光橙香水100ML</t>
+  </si>
+  <si>
+    <t>2023-03-01</t>
+  </si>
+  <si>
+    <t>【百补品牌热销40.6万件】GUCCI/古驰炼金士花园系列香水100ML正品香氛送礼</t>
+  </si>
+  <si>
+    <t>Maison Margiela 梅森马吉拉马丁马吉拉香水 慵懒周末/沙滩漫步【5天内发货】</t>
+  </si>
+  <si>
+    <t>马丁马吉拉-爵士酒廊淡香100ml</t>
+  </si>
+  <si>
+    <t>已选: 温暖壁炉/壁炉火光100ml</t>
+  </si>
+  <si>
+    <t>YSL新款爱心唇釉610#</t>
+  </si>
+  <si>
+    <t>已选: 610 冰乌龙</t>
+  </si>
+  <si>
+    <t>【BVLGARI】宝格丽 白茶 香水 茶香系列 淡香水EDT 75ml/150ml</t>
+  </si>
+  <si>
+    <t>宝格丽白茶淡香150ml</t>
+  </si>
+  <si>
+    <t>2025-11-22</t>
+  </si>
+  <si>
+    <t>已选: 150mL 宝格丽白茶</t>
+  </si>
+  <si>
+    <t>【宝格丽】悠境白茶淡香75ml正装新款白茶清新茶香木质花香</t>
+  </si>
+  <si>
+    <t>2022-10-14</t>
+  </si>
+  <si>
+    <t>【宝格丽】宝格丽白茶香水 淡香水 150ml/5oz【5天内发货】</t>
+  </si>
+  <si>
+    <t>已选: 150mL</t>
+  </si>
+  <si>
+    <t>【正品行货】植村秀绿茶卸妆洁颜油  温和深层清洁彩妆保湿</t>
+  </si>
+  <si>
+    <t>植村秀绿茶卸妆油150ml</t>
+  </si>
+  <si>
+    <t>2025-02-08</t>
+  </si>
+  <si>
+    <t>【正品行货】植村秀绿茶新肌洁颜油卸妆油150ml 去黄抗氧化</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>134.0</t>
+  </si>
+  <si>
+    <t>24.57</t>
+  </si>
+  <si>
+    <t>218.0</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>232.0</t>
+  </si>
+  <si>
+    <t>152.0</t>
+  </si>
+  <si>
+    <t>245</t>
+  </si>
+  <si>
+    <t>195.0</t>
+  </si>
+  <si>
+    <t>119.0</t>
+  </si>
+  <si>
+    <t>158.0</t>
+  </si>
+  <si>
+    <t>98.9</t>
+  </si>
+  <si>
+    <t>300.0</t>
+  </si>
+  <si>
+    <t>183.0</t>
+  </si>
+  <si>
+    <t>149</t>
+  </si>
+  <si>
+    <t>168</t>
+  </si>
+  <si>
+    <t>258.0</t>
+  </si>
+  <si>
+    <t>138.0</t>
+  </si>
+  <si>
+    <t>193.4</t>
+  </si>
+  <si>
+    <t>118.0</t>
+  </si>
+  <si>
+    <t>293.0</t>
+  </si>
+  <si>
+    <t>399.0</t>
+  </si>
+  <si>
+    <t>224.0</t>
+  </si>
+  <si>
+    <t>249.0</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>224</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>96.0</t>
+  </si>
+  <si>
+    <t>86.0</t>
+  </si>
+  <si>
+    <t>68.9</t>
+  </si>
+  <si>
+    <t>309.0</t>
+  </si>
+  <si>
+    <t>359.0</t>
+  </si>
+  <si>
+    <t>286</t>
   </si>
   <si>
     <t>299.0</t>
   </si>
   <si>
-    <t>202.0</t>
-  </si>
-  <si>
-    <t>200.0</t>
-  </si>
-  <si>
-    <t>183.9</t>
-  </si>
-  <si>
-    <t>192.0</t>
-  </si>
-  <si>
-    <t>1220.0</t>
-  </si>
-  <si>
-    <t>769.0</t>
-  </si>
-  <si>
-    <t>339.0</t>
-  </si>
-  <si>
-    <t>388.0</t>
-  </si>
-  <si>
-    <t>369.0</t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>145.0</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>258.0</t>
-  </si>
-  <si>
-    <t>162.0</t>
-  </si>
-  <si>
-    <t>201.0</t>
-  </si>
-  <si>
-    <t>288.0</t>
+    <t>169.0</t>
+  </si>
+  <si>
+    <t>119.9</t>
+  </si>
+  <si>
+    <t>599.0</t>
+  </si>
+  <si>
+    <t>368.0</t>
+  </si>
+  <si>
+    <t>同城用户刚刚拼成&amp;#10;可参与拼单马上拼</t>
+  </si>
+  <si>
+    <t>【6671人收藏】服装店袋子塑料袋购物袋礼品袋包装袋网红手提袋子服装店袋子批发</t>
+  </si>
+  <si>
+    <t>【清仓】筋膜球足底按摩球腰背部肌肉放松瑜伽肩颈腿膜健身筋膜球</t>
+  </si>
+  <si>
+    <t>1099.0</t>
+  </si>
+  <si>
+    <t>736.36</t>
+  </si>
+  <si>
+    <t>845.0</t>
+  </si>
+  <si>
+    <t>549.49</t>
+  </si>
+  <si>
+    <t>585</t>
+  </si>
+  <si>
+    <t>154.7</t>
+  </si>
+  <si>
+    <t>已优惠5元券后6.98已拼45.5万+件</t>
+  </si>
+  <si>
+    <t>899</t>
+  </si>
+  <si>
+    <t>6991.0</t>
+  </si>
+  <si>
+    <t>699.0</t>
+  </si>
+  <si>
+    <t>1026</t>
+  </si>
+  <si>
+    <t>380.0</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>38.0</t>
+  </si>
+  <si>
+    <t>【NARS】纳斯液体腮红BRAZEN西柚奶桃元气清透提气色易上色服帖持妆</t>
+  </si>
+  <si>
+    <t>NARS 水光绚色液体腮红 西柚奶桃 BRAZEN 7ml</t>
   </si>
   <si>
     <t>159.0</t>
   </si>
   <si>
-    <t>459.0</t>
-  </si>
-  <si>
-    <t>170.8</t>
-  </si>
-  <si>
-    <t>【百补品牌热销40.5万件】Gucci古驰绮梦馥栀女士EDP浓香水100ml 25年新品</t>
-  </si>
-  <si>
-    <t>GUCCI绮梦馥栀100ML</t>
-  </si>
-  <si>
-    <t>799.0</t>
-  </si>
-  <si>
-    <t>558.5</t>
-  </si>
-  <si>
-    <t>2025-09-17</t>
-  </si>
-  <si>
-    <t>【GUCCI】古驰绮梦馥栀香水100ml简装正品持久留香节日礼物自用</t>
-  </si>
-  <si>
-    <t>699.0</t>
-  </si>
-  <si>
-    <t>467.28</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>【正品行货】GUCCI古驰绮梦馥栀女士香水花香调简装无盖EDP 100ml</t>
-  </si>
-  <si>
-    <t>771.0</t>
-  </si>
-  <si>
-    <t>468.7</t>
-  </si>
-  <si>
-    <t>CPB滋润洗面奶125ml</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>89.9</t>
+  </si>
+  <si>
+    <t>已选: 7mL （24年4月批次） NARS液体腮红BRAZEN 西柚奶桃</t>
   </si>
 </sst>
 </file>
@@ -3867,19 +4970,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K668"/>
+  <dimension ref="A1:K897"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="5" style="5" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="3" max="3" width="33.33203125" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="9" width="33" customWidth="1"/>
-    <col min="10" max="10" width="50" customWidth="1"/>
+    <col min="9" max="9" width="24.83203125" customWidth="1"/>
+    <col min="10" max="10" width="38.33203125" customWidth="1"/>
     <col min="11" max="11" width="8" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4581,7 +5684,7 @@
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="1:11" ht="15">
+    <row r="25" spans="1:11" ht="30">
       <c r="A25" s="4">
         <v>14</v>
       </c>
@@ -6867,7 +7970,7 @@
         <v>377.88</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="30">
+    <row r="105" spans="1:11" ht="45">
       <c r="A105" s="4">
         <v>50</v>
       </c>
@@ -12698,7 +13801,7 @@
       <c r="J309" s="2"/>
       <c r="K309" s="2"/>
     </row>
-    <row r="310" spans="1:11" ht="15">
+    <row r="310" spans="1:11" ht="30">
       <c r="A310" s="4">
         <v>151</v>
       </c>
@@ -12750,7 +13853,7 @@
       <c r="J311" s="2"/>
       <c r="K311" s="2"/>
     </row>
-    <row r="312" spans="1:11" ht="15">
+    <row r="312" spans="1:11" ht="30">
       <c r="A312" s="4">
         <v>151</v>
       </c>
@@ -12806,7 +13909,7 @@
       <c r="J313" s="2"/>
       <c r="K313" s="2"/>
     </row>
-    <row r="314" spans="1:11" ht="15">
+    <row r="314" spans="1:11" ht="30">
       <c r="A314" s="4">
         <v>152</v>
       </c>
@@ -18589,7 +19692,7 @@
       <c r="J520" s="2"/>
       <c r="K520" s="2"/>
     </row>
-    <row r="521" spans="1:11" ht="15">
+    <row r="521" spans="1:11" ht="30">
       <c r="A521" s="4">
         <v>241</v>
       </c>
@@ -18618,7 +19721,7 @@
       <c r="J521" s="2"/>
       <c r="K521" s="2"/>
     </row>
-    <row r="522" spans="1:11" ht="15">
+    <row r="522" spans="1:11" ht="30">
       <c r="A522" s="4">
         <v>241</v>
       </c>
@@ -18865,7 +19968,7 @@
       <c r="J530" s="2"/>
       <c r="K530" s="2"/>
     </row>
-    <row r="531" spans="1:11" ht="15">
+    <row r="531" spans="1:11" ht="30">
       <c r="A531" s="4">
         <v>244</v>
       </c>
@@ -19153,7 +20256,7 @@
       <c r="J540" s="2"/>
       <c r="K540" s="2"/>
     </row>
-    <row r="541" spans="1:11" ht="15">
+    <row r="541" spans="1:11" ht="30">
       <c r="A541" s="4">
         <v>252</v>
       </c>
@@ -19894,7 +20997,7 @@
         <v>974</v>
       </c>
       <c r="C566" s="2" t="s">
-        <v>1150</v>
+        <v>973</v>
       </c>
       <c r="D566" s="2"/>
       <c r="E566" s="2">
@@ -22150,89 +23253,83 @@
     </row>
     <row r="644" spans="1:11" ht="30">
       <c r="A644" s="4">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>1073</v>
+        <v>1113</v>
       </c>
       <c r="C644" s="2" t="s">
-        <v>1074</v>
-      </c>
-      <c r="D644" s="2"/>
-      <c r="E644" s="2" t="s">
-        <v>1113</v>
+        <v>1114</v>
+      </c>
+      <c r="D644" s="2">
+        <v>799</v>
+      </c>
+      <c r="E644" s="2">
+        <v>558.5</v>
       </c>
       <c r="F644" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G644" s="2" t="s">
-        <v>568</v>
+        <v>1115</v>
       </c>
       <c r="H644" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I644" s="2"/>
-      <c r="J644" s="2" t="s">
-        <v>1075</v>
-      </c>
-      <c r="K644" s="2" t="s">
-        <v>1113</v>
-      </c>
+      <c r="J644" s="2"/>
+      <c r="K644" s="2"/>
     </row>
     <row r="645" spans="1:11" ht="30">
       <c r="A645" s="4">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>1076</v>
+        <v>1116</v>
       </c>
       <c r="C645" s="2" t="s">
-        <v>1074</v>
-      </c>
-      <c r="D645" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="E645" s="2" t="s">
-        <v>1115</v>
+      <c r="D645" s="2">
+        <v>699</v>
+      </c>
+      <c r="E645" s="2">
+        <v>467.28</v>
       </c>
       <c r="F645" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G645" s="2" t="s">
-        <v>568</v>
+        <v>1117</v>
       </c>
       <c r="H645" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I645" s="2"/>
-      <c r="J645" s="2" t="s">
-        <v>1077</v>
-      </c>
-      <c r="K645" s="2" t="s">
-        <v>1115</v>
-      </c>
-    </row>
-    <row r="646" spans="1:11" ht="15">
+      <c r="J645" s="2"/>
+      <c r="K645" s="2"/>
+    </row>
+    <row r="646" spans="1:11" ht="30">
       <c r="A646" s="4">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>1078</v>
+        <v>1118</v>
       </c>
       <c r="C646" s="2" t="s">
-        <v>1079</v>
-      </c>
-      <c r="D646" s="2" t="s">
-        <v>1116</v>
-      </c>
-      <c r="E646" s="2" t="s">
-        <v>1117</v>
+        <v>1114</v>
+      </c>
+      <c r="D646" s="2">
+        <v>771</v>
+      </c>
+      <c r="E646" s="2">
+        <v>468.7</v>
       </c>
       <c r="F646" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G646" s="2" t="s">
-        <v>30</v>
+        <v>884</v>
       </c>
       <c r="H646" s="2" t="s">
         <v>15</v>
@@ -22241,28 +23338,24 @@
       <c r="J646" s="2"/>
       <c r="K646" s="2"/>
     </row>
-    <row r="647" spans="1:11" ht="15">
+    <row r="647" spans="1:11" ht="30">
       <c r="A647" s="4">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>1080</v>
+        <v>1119</v>
       </c>
       <c r="C647" s="2" t="s">
-        <v>1079</v>
-      </c>
-      <c r="D647" s="2" t="s">
-        <v>1118</v>
-      </c>
-      <c r="E647" s="2" t="s">
-        <v>1119</v>
+        <v>1120</v>
+      </c>
+      <c r="D647" s="2"/>
+      <c r="E647" s="2">
+        <v>852</v>
       </c>
       <c r="F647" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G647" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="G647" s="2"/>
       <c r="H647" s="2" t="s">
         <v>15</v>
       </c>
@@ -22272,25 +23365,25 @@
     </row>
     <row r="648" spans="1:11" ht="30">
       <c r="A648" s="4">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>1081</v>
+        <v>1121</v>
       </c>
       <c r="C648" s="2" t="s">
-        <v>1079</v>
-      </c>
-      <c r="D648" s="2" t="s">
-        <v>1114</v>
-      </c>
-      <c r="E648" s="2" t="s">
         <v>1120</v>
       </c>
+      <c r="D648" s="2">
+        <v>538</v>
+      </c>
+      <c r="E648" s="2">
+        <v>339</v>
+      </c>
       <c r="F648" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G648" s="2" t="s">
-        <v>55</v>
+        <v>620</v>
       </c>
       <c r="H648" s="2" t="s">
         <v>15</v>
@@ -22299,27 +23392,25 @@
       <c r="J648" s="2"/>
       <c r="K648" s="2"/>
     </row>
-    <row r="649" spans="1:11" ht="30">
+    <row r="649" spans="1:11" ht="15">
       <c r="A649" s="4">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>1082</v>
+        <v>1122</v>
       </c>
       <c r="C649" s="2" t="s">
-        <v>1079</v>
-      </c>
-      <c r="D649" s="2" t="s">
-        <v>1116</v>
-      </c>
-      <c r="E649" s="2" t="s">
-        <v>1120</v>
+        <v>1123</v>
+      </c>
+      <c r="D649" s="2"/>
+      <c r="E649" s="2">
+        <v>888</v>
       </c>
       <c r="F649" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G649" s="2" t="s">
-        <v>425</v>
+        <v>1124</v>
       </c>
       <c r="H649" s="2" t="s">
         <v>15</v>
@@ -22330,107 +23421,117 @@
     </row>
     <row r="650" spans="1:11" ht="30">
       <c r="A650" s="4">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>854</v>
+        <v>1118</v>
       </c>
       <c r="C650" s="2" t="s">
-        <v>1083</v>
-      </c>
-      <c r="D650" s="2" t="s">
-        <v>1121</v>
-      </c>
-      <c r="E650" s="2" t="s">
-        <v>1122</v>
+        <v>1125</v>
+      </c>
+      <c r="D650" s="2">
+        <v>771</v>
+      </c>
+      <c r="E650" s="2">
+        <v>468.7</v>
       </c>
       <c r="F650" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G650" s="2" t="s">
-        <v>855</v>
+        <v>884</v>
       </c>
       <c r="H650" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I650" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="I650" s="2" t="s">
+        <v>604</v>
+      </c>
       <c r="J650" s="2"/>
       <c r="K650" s="2"/>
     </row>
-    <row r="651" spans="1:11" ht="30">
+    <row r="651" spans="1:11" ht="15">
       <c r="A651" s="4">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>1084</v>
+        <v>1126</v>
       </c>
       <c r="C651" s="2" t="s">
-        <v>1085</v>
-      </c>
-      <c r="D651" s="2"/>
-      <c r="E651" s="2" t="s">
-        <v>1123</v>
+        <v>1125</v>
+      </c>
+      <c r="D651" s="2">
+        <v>799</v>
+      </c>
+      <c r="E651" s="2">
+        <v>531</v>
       </c>
       <c r="F651" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G651" s="2" t="s">
-        <v>48</v>
+        <v>1115</v>
       </c>
       <c r="H651" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I651" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="I651" s="2" t="s">
+        <v>604</v>
+      </c>
       <c r="J651" s="2"/>
       <c r="K651" s="2"/>
     </row>
     <row r="652" spans="1:11" ht="30">
       <c r="A652" s="4">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B652" s="2" t="s">
-        <v>1086</v>
+        <v>1116</v>
       </c>
       <c r="C652" s="2" t="s">
-        <v>1085</v>
-      </c>
-      <c r="D652" s="2"/>
-      <c r="E652" s="2" t="s">
-        <v>1124</v>
+        <v>1125</v>
+      </c>
+      <c r="D652" s="2">
+        <v>699</v>
+      </c>
+      <c r="E652" s="2">
+        <v>467.28</v>
       </c>
       <c r="F652" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G652" s="2" t="s">
-        <v>441</v>
+        <v>1117</v>
       </c>
       <c r="H652" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I652" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="I652" s="2" t="s">
+        <v>604</v>
+      </c>
       <c r="J652" s="2"/>
       <c r="K652" s="2"/>
     </row>
     <row r="653" spans="1:11" ht="15">
       <c r="A653" s="4">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>1087</v>
+        <v>1127</v>
       </c>
       <c r="C653" s="2" t="s">
-        <v>1085</v>
-      </c>
-      <c r="D653" s="2"/>
-      <c r="E653" s="2" t="s">
-        <v>1124</v>
+        <v>1125</v>
+      </c>
+      <c r="D653" s="2">
+        <v>699</v>
+      </c>
+      <c r="E653" s="2">
+        <v>432</v>
       </c>
       <c r="F653" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G653" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="G653" s="2"/>
       <c r="H653" s="2" t="s">
         <v>15</v>
       </c>
@@ -22440,75 +23541,75 @@
     </row>
     <row r="654" spans="1:11" ht="30">
       <c r="A654" s="4">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>1088</v>
+        <v>1128</v>
       </c>
       <c r="C654" s="2" t="s">
-        <v>1085</v>
+        <v>1129</v>
       </c>
       <c r="D654" s="2"/>
-      <c r="E654" s="2" t="s">
-        <v>1125</v>
+      <c r="E654" s="2">
+        <v>603</v>
       </c>
       <c r="F654" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G654" s="2" t="s">
-        <v>1089</v>
+        <v>118</v>
       </c>
       <c r="H654" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I654" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="I654" s="2" t="s">
+        <v>89</v>
+      </c>
       <c r="J654" s="2"/>
       <c r="K654" s="2"/>
     </row>
-    <row r="655" spans="1:11" ht="30">
+    <row r="655" spans="1:11" ht="15">
       <c r="A655" s="4">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>1090</v>
+        <v>1122</v>
       </c>
       <c r="C655" s="2" t="s">
-        <v>1091</v>
+        <v>1129</v>
       </c>
       <c r="D655" s="2"/>
-      <c r="E655" s="2" t="s">
-        <v>1126</v>
+      <c r="E655" s="2">
+        <v>888</v>
       </c>
       <c r="F655" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G655" s="2"/>
+      <c r="G655" s="2" t="s">
+        <v>1124</v>
+      </c>
       <c r="H655" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I655" s="2"/>
-      <c r="J655" s="2" t="s">
-        <v>1092</v>
-      </c>
-      <c r="K655" s="2" t="s">
-        <v>1126</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="I655" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="J655" s="2"/>
+      <c r="K655" s="2"/>
     </row>
     <row r="656" spans="1:11" ht="30">
       <c r="A656" s="4">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="B656" s="2" t="s">
-        <v>1093</v>
+        <v>1131</v>
       </c>
       <c r="C656" s="2" t="s">
-        <v>1091</v>
-      </c>
-      <c r="D656" s="2" t="s">
-        <v>1127</v>
-      </c>
-      <c r="E656" s="2" t="s">
-        <v>1128</v>
+        <v>1129</v>
+      </c>
+      <c r="D656" s="2"/>
+      <c r="E656" s="2">
+        <v>650</v>
       </c>
       <c r="F656" s="2" t="s">
         <v>13</v>
@@ -22519,25 +23620,25 @@
       </c>
       <c r="I656" s="2"/>
       <c r="J656" s="2" t="s">
-        <v>1094</v>
-      </c>
-      <c r="K656" s="2" t="s">
-        <v>1128</v>
+        <v>1132</v>
+      </c>
+      <c r="K656" s="2">
+        <v>650</v>
       </c>
     </row>
     <row r="657" spans="1:11" ht="30">
       <c r="A657" s="4">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="B657" s="2" t="s">
-        <v>1095</v>
+        <v>1133</v>
       </c>
       <c r="C657" s="2" t="s">
-        <v>1091</v>
+        <v>1129</v>
       </c>
       <c r="D657" s="2"/>
-      <c r="E657" s="2" t="s">
-        <v>1129</v>
+      <c r="E657" s="2">
+        <v>532</v>
       </c>
       <c r="F657" s="2" t="s">
         <v>13</v>
@@ -22548,83 +23649,81 @@
       </c>
       <c r="I657" s="2"/>
       <c r="J657" s="2" t="s">
-        <v>1096</v>
-      </c>
-      <c r="K657" s="2" t="s">
-        <v>1129</v>
+        <v>1134</v>
+      </c>
+      <c r="K657" s="2">
+        <v>532</v>
       </c>
     </row>
     <row r="658" spans="1:11" ht="30">
       <c r="A658" s="4">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="B658" s="2" t="s">
-        <v>1097</v>
+        <v>1135</v>
       </c>
       <c r="C658" s="2" t="s">
-        <v>1098</v>
+        <v>1129</v>
       </c>
       <c r="D658" s="2"/>
-      <c r="E658" s="2" t="s">
-        <v>1126</v>
+      <c r="E658" s="2">
+        <v>256</v>
       </c>
       <c r="F658" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G658" s="2"/>
       <c r="H658" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I658" s="2"/>
-      <c r="J658" s="2" t="s">
-        <v>1099</v>
-      </c>
-      <c r="K658" s="2" t="s">
-        <v>1126</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="I658" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J658" s="2"/>
+      <c r="K658" s="2"/>
     </row>
     <row r="659" spans="1:11" ht="30">
       <c r="A659" s="4">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="B659" s="2" t="s">
-        <v>1100</v>
+        <v>1136</v>
       </c>
       <c r="C659" s="2" t="s">
-        <v>1098</v>
+        <v>1137</v>
       </c>
       <c r="D659" s="2"/>
-      <c r="E659" s="2" t="s">
-        <v>1130</v>
+      <c r="E659" s="2">
+        <v>455</v>
       </c>
       <c r="F659" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G659" s="2"/>
+      <c r="G659" s="2" t="s">
+        <v>1138</v>
+      </c>
       <c r="H659" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I659" s="2"/>
-      <c r="J659" s="2" t="s">
-        <v>1101</v>
-      </c>
-      <c r="K659" s="2" t="s">
-        <v>1130</v>
-      </c>
+      <c r="J659" s="2"/>
+      <c r="K659" s="2"/>
     </row>
     <row r="660" spans="1:11" ht="30">
       <c r="A660" s="4">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="B660" s="2" t="s">
-        <v>1102</v>
+        <v>1139</v>
       </c>
       <c r="C660" s="2" t="s">
-        <v>1098</v>
-      </c>
-      <c r="D660" s="2"/>
-      <c r="E660" s="2" t="s">
-        <v>1130</v>
+        <v>1140</v>
+      </c>
+      <c r="D660" s="2">
+        <v>318.98</v>
+      </c>
+      <c r="E660" s="2">
+        <v>317.98</v>
       </c>
       <c r="F660" s="2" t="s">
         <v>13</v>
@@ -22635,62 +23734,62 @@
       </c>
       <c r="I660" s="2"/>
       <c r="J660" s="2" t="s">
-        <v>1103</v>
-      </c>
-      <c r="K660" s="2" t="s">
-        <v>1130</v>
+        <v>1141</v>
+      </c>
+      <c r="K660" s="2">
+        <v>317.98</v>
       </c>
     </row>
     <row r="661" spans="1:11" ht="30">
       <c r="A661" s="4">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="B661" s="2" t="s">
-        <v>1104</v>
+        <v>1142</v>
       </c>
       <c r="C661" s="2" t="s">
-        <v>1105</v>
-      </c>
-      <c r="D661" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="E661" s="2" t="s">
-        <v>1132</v>
+        <v>1143</v>
+      </c>
+      <c r="D661" s="2">
+        <v>1099</v>
+      </c>
+      <c r="E661" s="2">
+        <v>672</v>
       </c>
       <c r="F661" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G661" s="2"/>
+      <c r="G661" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="H661" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I661" s="2" t="s">
-        <v>89</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I661" s="2"/>
       <c r="J661" s="2"/>
       <c r="K661" s="2"/>
     </row>
     <row r="662" spans="1:11" ht="30">
       <c r="A662" s="4">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>1106</v>
+        <v>1144</v>
       </c>
       <c r="C662" s="2" t="s">
-        <v>1107</v>
-      </c>
-      <c r="D662" s="2" t="s">
-        <v>1116</v>
-      </c>
-      <c r="E662" s="2" t="s">
-        <v>1133</v>
+        <v>1143</v>
+      </c>
+      <c r="D662" s="2">
+        <v>1216</v>
+      </c>
+      <c r="E662" s="2">
+        <v>749</v>
       </c>
       <c r="F662" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G662" s="2" t="s">
-        <v>274</v>
+        <v>430</v>
       </c>
       <c r="H662" s="2" t="s">
         <v>15</v>
@@ -22699,52 +23798,60 @@
       <c r="J662" s="2"/>
       <c r="K662" s="2"/>
     </row>
-    <row r="663" spans="1:11" ht="15">
+    <row r="663" spans="1:11" ht="30">
       <c r="A663" s="4">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>1108</v>
+        <v>1145</v>
       </c>
       <c r="C663" s="2" t="s">
-        <v>1109</v>
-      </c>
-      <c r="D663" s="2" t="s">
-        <v>1134</v>
-      </c>
-      <c r="E663" s="2" t="s">
-        <v>1135</v>
+        <v>1146</v>
+      </c>
+      <c r="D663" s="2">
+        <v>1359</v>
+      </c>
+      <c r="E663" s="2">
+        <v>989</v>
       </c>
       <c r="F663" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G663" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="G663" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="H663" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I663" s="2"/>
-      <c r="J663" s="2"/>
-      <c r="K663" s="2"/>
-    </row>
-    <row r="664" spans="1:11" ht="15">
+      <c r="J663" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K663" s="2">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="664" spans="1:11" ht="30">
       <c r="A664" s="4">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="B664" s="2" t="s">
-        <v>1110</v>
+        <v>1148</v>
       </c>
       <c r="C664" s="2" t="s">
-        <v>1109</v>
-      </c>
-      <c r="D664" s="2"/>
-      <c r="E664" s="2" t="s">
-        <v>1136</v>
+        <v>1146</v>
+      </c>
+      <c r="D664" s="2">
+        <v>699</v>
+      </c>
+      <c r="E664" s="2">
+        <v>462</v>
       </c>
       <c r="F664" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G664" s="2" t="s">
-        <v>425</v>
+        <v>30</v>
       </c>
       <c r="H664" s="2" t="s">
         <v>15</v>
@@ -22755,24 +23862,26 @@
     </row>
     <row r="665" spans="1:11" ht="30">
       <c r="A665" s="4">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>1111</v>
+        <v>1149</v>
       </c>
       <c r="C665" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D665" s="2" t="s">
-        <v>1116</v>
-      </c>
-      <c r="E665" s="2" t="s">
-        <v>1137</v>
+        <v>1146</v>
+      </c>
+      <c r="D665" s="2">
+        <v>896</v>
+      </c>
+      <c r="E665" s="2">
+        <v>556</v>
       </c>
       <c r="F665" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G665" s="2"/>
+      <c r="G665" s="2" t="s">
+        <v>430</v>
+      </c>
       <c r="H665" s="2" t="s">
         <v>15</v>
       </c>
@@ -22782,25 +23891,25 @@
     </row>
     <row r="666" spans="1:11" ht="30">
       <c r="A666" s="4">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>1138</v>
+        <v>1150</v>
       </c>
       <c r="C666" s="2" t="s">
-        <v>1139</v>
-      </c>
-      <c r="D666" s="2" t="s">
-        <v>1140</v>
-      </c>
-      <c r="E666" s="2" t="s">
-        <v>1141</v>
+        <v>1151</v>
+      </c>
+      <c r="D666" s="2">
+        <v>1213</v>
+      </c>
+      <c r="E666" s="2">
+        <v>825</v>
       </c>
       <c r="F666" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G666" s="2" t="s">
-        <v>1142</v>
+        <v>1152</v>
       </c>
       <c r="H666" s="2" t="s">
         <v>15</v>
@@ -22811,61 +23920,6706 @@
     </row>
     <row r="667" spans="1:11" ht="30">
       <c r="A667" s="4">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>1143</v>
+        <v>996</v>
       </c>
       <c r="C667" s="2" t="s">
-        <v>1139</v>
-      </c>
-      <c r="D667" s="2" t="s">
-        <v>1144</v>
-      </c>
-      <c r="E667" s="2" t="s">
-        <v>1145</v>
+        <v>1153</v>
+      </c>
+      <c r="D667" s="2">
+        <v>600</v>
+      </c>
+      <c r="E667" s="2">
+        <v>432</v>
       </c>
       <c r="F667" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G667" s="2" t="s">
-        <v>1146</v>
+        <v>998</v>
       </c>
       <c r="H667" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I667" s="2"/>
-      <c r="J667" s="2"/>
-      <c r="K667" s="2"/>
-    </row>
-    <row r="668" spans="1:11" ht="30">
+      <c r="J667" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="K667" s="2">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="668" spans="1:11" ht="15">
       <c r="A668" s="4">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>1147</v>
+        <v>1154</v>
       </c>
       <c r="C668" s="2" t="s">
-        <v>1139</v>
-      </c>
-      <c r="D668" s="2" t="s">
-        <v>1148</v>
-      </c>
-      <c r="E668" s="2" t="s">
-        <v>1149</v>
+        <v>1155</v>
+      </c>
+      <c r="D668" s="2">
+        <v>339</v>
+      </c>
+      <c r="E668" s="2">
+        <v>229</v>
       </c>
       <c r="F668" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G668" s="2" t="s">
-        <v>884</v>
-      </c>
+      <c r="G668" s="2"/>
       <c r="H668" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I668" s="2"/>
       <c r="J668" s="2"/>
       <c r="K668" s="2"/>
+    </row>
+    <row r="669" spans="1:11" ht="30">
+      <c r="A669" s="4">
+        <v>313</v>
+      </c>
+      <c r="B669" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C669" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D669" s="2">
+        <v>393</v>
+      </c>
+      <c r="E669" s="2">
+        <v>244</v>
+      </c>
+      <c r="F669" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G669" s="2"/>
+      <c r="H669" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I669" s="2"/>
+      <c r="J669" s="2"/>
+      <c r="K669" s="2"/>
+    </row>
+    <row r="670" spans="1:11" ht="30">
+      <c r="A670" s="4">
+        <v>313</v>
+      </c>
+      <c r="B670" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C670" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D670" s="2">
+        <v>354</v>
+      </c>
+      <c r="E670" s="2">
+        <v>220</v>
+      </c>
+      <c r="F670" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G670" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H670" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I670" s="2"/>
+      <c r="J670" s="2"/>
+      <c r="K670" s="2"/>
+    </row>
+    <row r="671" spans="1:11" ht="30">
+      <c r="A671" s="4">
+        <v>314</v>
+      </c>
+      <c r="B671" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C671" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D671" s="2">
+        <v>699</v>
+      </c>
+      <c r="E671" s="2">
+        <v>494</v>
+      </c>
+      <c r="F671" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G671" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="H671" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I671" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J671" s="2"/>
+      <c r="K671" s="2"/>
+    </row>
+    <row r="672" spans="1:11" ht="30">
+      <c r="A672" s="4">
+        <v>314</v>
+      </c>
+      <c r="B672" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C672" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D672" s="2">
+        <v>998</v>
+      </c>
+      <c r="E672" s="2">
+        <v>695</v>
+      </c>
+      <c r="F672" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G672" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H672" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I672" s="2"/>
+      <c r="J672" s="2"/>
+      <c r="K672" s="2"/>
+    </row>
+    <row r="673" spans="1:11" ht="30">
+      <c r="A673" s="4">
+        <v>315</v>
+      </c>
+      <c r="B673" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C673" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D673" s="2">
+        <v>998</v>
+      </c>
+      <c r="E673" s="2">
+        <v>695</v>
+      </c>
+      <c r="F673" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G673" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H673" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I673" s="2"/>
+      <c r="J673" s="2"/>
+      <c r="K673" s="2"/>
+    </row>
+    <row r="674" spans="1:11" ht="15">
+      <c r="A674" s="4">
+        <v>315</v>
+      </c>
+      <c r="B674" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C674" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D674" s="2">
+        <v>699</v>
+      </c>
+      <c r="E674" s="2">
+        <v>545</v>
+      </c>
+      <c r="F674" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G674" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H674" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I674" s="2"/>
+      <c r="J674" s="2"/>
+      <c r="K674" s="2"/>
+    </row>
+    <row r="675" spans="1:11" ht="30">
+      <c r="A675" s="4">
+        <v>315</v>
+      </c>
+      <c r="B675" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C675" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D675" s="2">
+        <v>699</v>
+      </c>
+      <c r="E675" s="2">
+        <v>494</v>
+      </c>
+      <c r="F675" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G675" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="H675" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I675" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J675" s="2"/>
+      <c r="K675" s="2"/>
+    </row>
+    <row r="676" spans="1:11" ht="30">
+      <c r="A676" s="4">
+        <v>316</v>
+      </c>
+      <c r="B676" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C676" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D676" s="2">
+        <v>1048</v>
+      </c>
+      <c r="E676" s="2">
+        <v>701</v>
+      </c>
+      <c r="F676" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G676" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H676" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I676" s="2"/>
+      <c r="J676" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="K676" s="2">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="677" spans="1:11" ht="15">
+      <c r="A677" s="4">
+        <v>316</v>
+      </c>
+      <c r="B677" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C677" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D677" s="2">
+        <v>868</v>
+      </c>
+      <c r="E677" s="2">
+        <v>577</v>
+      </c>
+      <c r="F677" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G677" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H677" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I677" s="2"/>
+      <c r="J677" s="2"/>
+      <c r="K677" s="2"/>
+    </row>
+    <row r="678" spans="1:11" ht="15">
+      <c r="A678" s="4">
+        <v>316</v>
+      </c>
+      <c r="B678" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C678" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D678" s="2">
+        <v>870</v>
+      </c>
+      <c r="E678" s="2">
+        <v>643</v>
+      </c>
+      <c r="F678" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G678" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="H678" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I678" s="2"/>
+      <c r="J678" s="2"/>
+      <c r="K678" s="2"/>
+    </row>
+    <row r="679" spans="1:11" ht="15">
+      <c r="A679" s="4">
+        <v>316</v>
+      </c>
+      <c r="B679" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C679" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D679" s="2">
+        <v>879</v>
+      </c>
+      <c r="E679" s="2">
+        <v>679</v>
+      </c>
+      <c r="F679" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G679" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="H679" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I679" s="2"/>
+      <c r="J679" s="2"/>
+      <c r="K679" s="2"/>
+    </row>
+    <row r="680" spans="1:11" ht="15">
+      <c r="A680" s="4">
+        <v>317</v>
+      </c>
+      <c r="B680" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C680" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D680" s="2"/>
+      <c r="E680" s="2">
+        <v>129</v>
+      </c>
+      <c r="F680" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G680" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H680" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I680" s="2"/>
+      <c r="J680" s="2"/>
+      <c r="K680" s="2"/>
+    </row>
+    <row r="681" spans="1:11" ht="30">
+      <c r="A681" s="4">
+        <v>317</v>
+      </c>
+      <c r="B681" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C681" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D681" s="2"/>
+      <c r="E681" s="2">
+        <v>69.8</v>
+      </c>
+      <c r="F681" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G681" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H681" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I681" s="2"/>
+      <c r="J681" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="K681" s="2">
+        <v>69.8</v>
+      </c>
+    </row>
+    <row r="682" spans="1:11" ht="30">
+      <c r="A682" s="4">
+        <v>317</v>
+      </c>
+      <c r="B682" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C682" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D682" s="2"/>
+      <c r="E682" s="2">
+        <v>119</v>
+      </c>
+      <c r="F682" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G682" s="2"/>
+      <c r="H682" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I682" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="J682" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="K682" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="683" spans="1:11" ht="30">
+      <c r="A683" s="4">
+        <v>317</v>
+      </c>
+      <c r="B683" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C683" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D683" s="2">
+        <v>199</v>
+      </c>
+      <c r="E683" s="2">
+        <v>118.99</v>
+      </c>
+      <c r="F683" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G683" s="2"/>
+      <c r="H683" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I683" s="2"/>
+      <c r="J683" s="2"/>
+      <c r="K683" s="2"/>
+    </row>
+    <row r="684" spans="1:11" ht="30">
+      <c r="A684" s="4">
+        <v>318</v>
+      </c>
+      <c r="B684" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C684" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D684" s="2">
+        <v>255</v>
+      </c>
+      <c r="E684" s="2">
+        <v>245</v>
+      </c>
+      <c r="F684" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G684" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="H684" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I684" s="2"/>
+      <c r="J684" s="2"/>
+      <c r="K684" s="2"/>
+    </row>
+    <row r="685" spans="1:11" ht="15">
+      <c r="A685" s="4">
+        <v>318</v>
+      </c>
+      <c r="B685" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C685" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D685" s="2">
+        <v>785</v>
+      </c>
+      <c r="E685" s="2">
+        <v>472.9</v>
+      </c>
+      <c r="F685" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G685" s="2"/>
+      <c r="H685" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I685" s="2"/>
+      <c r="J685" s="2"/>
+      <c r="K685" s="2"/>
+    </row>
+    <row r="686" spans="1:11" ht="30">
+      <c r="A686" s="4">
+        <v>319</v>
+      </c>
+      <c r="B686" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C686" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D686" s="2">
+        <v>222</v>
+      </c>
+      <c r="E686" s="2">
+        <v>146</v>
+      </c>
+      <c r="F686" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G686" s="2"/>
+      <c r="H686" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I686" s="2"/>
+      <c r="J686" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="K686" s="2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="687" spans="1:11" ht="30">
+      <c r="A687" s="4">
+        <v>320</v>
+      </c>
+      <c r="B687" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C687" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D687" s="2">
+        <v>94.87</v>
+      </c>
+      <c r="E687" s="2">
+        <v>72.5</v>
+      </c>
+      <c r="F687" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G687" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H687" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I687" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="J687" s="2"/>
+      <c r="K687" s="2"/>
+    </row>
+    <row r="688" spans="1:11" ht="30">
+      <c r="A688" s="4">
+        <v>320</v>
+      </c>
+      <c r="B688" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C688" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D688" s="2">
+        <v>700</v>
+      </c>
+      <c r="E688" s="2">
+        <v>440</v>
+      </c>
+      <c r="F688" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G688" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H688" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I688" s="2"/>
+      <c r="J688" s="2"/>
+      <c r="K688" s="2"/>
+    </row>
+    <row r="689" spans="1:11" ht="30">
+      <c r="A689" s="4">
+        <v>320</v>
+      </c>
+      <c r="B689" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C689" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D689" s="2">
+        <v>380</v>
+      </c>
+      <c r="E689" s="2">
+        <v>236</v>
+      </c>
+      <c r="F689" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G689" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H689" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I689" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="J689" s="2"/>
+      <c r="K689" s="2"/>
+    </row>
+    <row r="690" spans="1:11" ht="30">
+      <c r="A690" s="4">
+        <v>321</v>
+      </c>
+      <c r="B690" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C690" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D690" s="2">
+        <v>1213</v>
+      </c>
+      <c r="E690" s="2">
+        <v>825</v>
+      </c>
+      <c r="F690" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G690" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="H690" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I690" s="2"/>
+      <c r="J690" s="2"/>
+      <c r="K690" s="2"/>
+    </row>
+    <row r="691" spans="1:11" ht="30">
+      <c r="A691" s="4">
+        <v>322</v>
+      </c>
+      <c r="B691" s="2" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C691" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D691" s="2"/>
+      <c r="E691" s="2">
+        <v>1398</v>
+      </c>
+      <c r="F691" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G691" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="H691" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I691" s="2"/>
+      <c r="J691" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="K691" s="2">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="692" spans="1:11" ht="30">
+      <c r="A692" s="4">
+        <v>323</v>
+      </c>
+      <c r="B692" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C692" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D692" s="2">
+        <v>393</v>
+      </c>
+      <c r="E692" s="2">
+        <v>244</v>
+      </c>
+      <c r="F692" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G692" s="2"/>
+      <c r="H692" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I692" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J692" s="2"/>
+      <c r="K692" s="2"/>
+    </row>
+    <row r="693" spans="1:11" ht="30">
+      <c r="A693" s="4">
+        <v>323</v>
+      </c>
+      <c r="B693" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C693" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D693" s="2">
+        <v>424</v>
+      </c>
+      <c r="E693" s="2">
+        <v>263</v>
+      </c>
+      <c r="F693" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G693" s="2"/>
+      <c r="H693" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I693" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J693" s="2"/>
+      <c r="K693" s="2"/>
+    </row>
+    <row r="694" spans="1:11" ht="30">
+      <c r="A694" s="4">
+        <v>323</v>
+      </c>
+      <c r="B694" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C694" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D694" s="2"/>
+      <c r="E694" s="2">
+        <v>299</v>
+      </c>
+      <c r="F694" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G694" s="2"/>
+      <c r="H694" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I694" s="2"/>
+      <c r="J694" s="2"/>
+      <c r="K694" s="2"/>
+    </row>
+    <row r="695" spans="1:11" ht="30">
+      <c r="A695" s="4">
+        <v>323</v>
+      </c>
+      <c r="B695" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C695" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D695" s="2"/>
+      <c r="E695" s="2">
+        <v>499</v>
+      </c>
+      <c r="F695" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G695" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="H695" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I695" s="2"/>
+      <c r="J695" s="2"/>
+      <c r="K695" s="2"/>
+    </row>
+    <row r="696" spans="1:11" ht="30">
+      <c r="A696" s="4">
+        <v>323</v>
+      </c>
+      <c r="B696" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C696" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D696" s="2"/>
+      <c r="E696" s="2">
+        <v>298</v>
+      </c>
+      <c r="F696" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G696" s="2"/>
+      <c r="H696" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I696" s="2"/>
+      <c r="J696" s="2"/>
+      <c r="K696" s="2"/>
+    </row>
+    <row r="697" spans="1:11" ht="15">
+      <c r="A697" s="4">
+        <v>324</v>
+      </c>
+      <c r="B697" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C697" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D697" s="2"/>
+      <c r="E697" s="2">
+        <v>113</v>
+      </c>
+      <c r="F697" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G697" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H697" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I697" s="2"/>
+      <c r="J697" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="K697" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="698" spans="1:11" ht="30">
+      <c r="A698" s="4">
+        <v>325</v>
+      </c>
+      <c r="B698" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C698" s="2" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D698" s="2"/>
+      <c r="E698" s="2">
+        <v>130.4</v>
+      </c>
+      <c r="F698" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G698" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H698" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I698" s="2"/>
+      <c r="J698" s="2"/>
+      <c r="K698" s="2"/>
+    </row>
+    <row r="699" spans="1:11" ht="30">
+      <c r="A699" s="4">
+        <v>325</v>
+      </c>
+      <c r="B699" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C699" s="2" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D699" s="2">
+        <v>235</v>
+      </c>
+      <c r="E699" s="2">
+        <v>156</v>
+      </c>
+      <c r="F699" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G699" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H699" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I699" s="2"/>
+      <c r="J699" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="K699" s="2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="700" spans="1:11" ht="15">
+      <c r="A700" s="4">
+        <v>325</v>
+      </c>
+      <c r="B700" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C700" s="2" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D700" s="2"/>
+      <c r="E700" s="2">
+        <v>143.4</v>
+      </c>
+      <c r="F700" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G700" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="H700" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I700" s="2"/>
+      <c r="J700" s="2"/>
+      <c r="K700" s="2"/>
+    </row>
+    <row r="701" spans="1:11" ht="30">
+      <c r="A701" s="4">
+        <v>325</v>
+      </c>
+      <c r="B701" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="C701" s="2" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D701" s="2">
+        <v>239</v>
+      </c>
+      <c r="E701" s="2">
+        <v>146</v>
+      </c>
+      <c r="F701" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G701" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="H701" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I701" s="2"/>
+      <c r="J701" s="2"/>
+      <c r="K701" s="2"/>
+    </row>
+    <row r="702" spans="1:11" ht="15">
+      <c r="A702" s="4">
+        <v>326</v>
+      </c>
+      <c r="B702" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C702" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D702" s="2">
+        <v>299</v>
+      </c>
+      <c r="E702" s="2">
+        <v>192.5</v>
+      </c>
+      <c r="F702" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G702" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H702" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I702" s="2"/>
+      <c r="J702" s="2"/>
+      <c r="K702" s="2"/>
+    </row>
+    <row r="703" spans="1:11" ht="15">
+      <c r="A703" s="4">
+        <v>326</v>
+      </c>
+      <c r="B703" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="C703" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D703" s="2">
+        <v>158</v>
+      </c>
+      <c r="E703" s="2">
+        <v>98.9</v>
+      </c>
+      <c r="F703" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G703" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H703" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I703" s="2"/>
+      <c r="J703" s="2"/>
+      <c r="K703" s="2"/>
+    </row>
+    <row r="704" spans="1:11" ht="15">
+      <c r="A704" s="4">
+        <v>327</v>
+      </c>
+      <c r="B704" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C704" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D704" s="2">
+        <v>259</v>
+      </c>
+      <c r="E704" s="2">
+        <v>158.84</v>
+      </c>
+      <c r="F704" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G704" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="H704" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I704" s="2"/>
+      <c r="J704" s="2"/>
+      <c r="K704" s="2"/>
+    </row>
+    <row r="705" spans="1:11" ht="15">
+      <c r="A705" s="4">
+        <v>327</v>
+      </c>
+      <c r="B705" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C705" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D705" s="2">
+        <v>234</v>
+      </c>
+      <c r="E705" s="2">
+        <v>143.15</v>
+      </c>
+      <c r="F705" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G705" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="H705" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I705" s="2"/>
+      <c r="J705" s="2"/>
+      <c r="K705" s="2"/>
+    </row>
+    <row r="706" spans="1:11" ht="30">
+      <c r="A706" s="4">
+        <v>328</v>
+      </c>
+      <c r="B706" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C706" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D706" s="2">
+        <v>1218</v>
+      </c>
+      <c r="E706" s="2">
+        <v>775</v>
+      </c>
+      <c r="F706" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G706" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H706" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I706" s="2"/>
+      <c r="J706" s="2"/>
+      <c r="K706" s="2"/>
+    </row>
+    <row r="707" spans="1:11" ht="30">
+      <c r="A707" s="4">
+        <v>328</v>
+      </c>
+      <c r="B707" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C707" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D707" s="2">
+        <v>1300</v>
+      </c>
+      <c r="E707" s="2">
+        <v>782</v>
+      </c>
+      <c r="F707" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G707" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H707" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I707" s="2"/>
+      <c r="J707" s="2"/>
+      <c r="K707" s="2"/>
+    </row>
+    <row r="708" spans="1:11" ht="30">
+      <c r="A708" s="4">
+        <v>329</v>
+      </c>
+      <c r="B708" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C708" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D708" s="2">
+        <v>1048</v>
+      </c>
+      <c r="E708" s="2">
+        <v>692</v>
+      </c>
+      <c r="F708" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G708" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H708" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I708" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J708" s="2"/>
+      <c r="K708" s="2"/>
+    </row>
+    <row r="709" spans="1:11" ht="30">
+      <c r="A709" s="4">
+        <v>329</v>
+      </c>
+      <c r="B709" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C709" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D709" s="2">
+        <v>998</v>
+      </c>
+      <c r="E709" s="2">
+        <v>860</v>
+      </c>
+      <c r="F709" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G709" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="H709" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I709" s="2"/>
+      <c r="J709" s="2"/>
+      <c r="K709" s="2"/>
+    </row>
+    <row r="710" spans="1:11" ht="15">
+      <c r="A710" s="4">
+        <v>330</v>
+      </c>
+      <c r="B710" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C710" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D710" s="2">
+        <v>115</v>
+      </c>
+      <c r="E710" s="2">
+        <v>99.5</v>
+      </c>
+      <c r="F710" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G710" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H710" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I710" s="2"/>
+      <c r="J710" s="2"/>
+      <c r="K710" s="2"/>
+    </row>
+    <row r="711" spans="1:11" ht="15">
+      <c r="A711" s="4">
+        <v>330</v>
+      </c>
+      <c r="B711" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C711" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D711" s="2"/>
+      <c r="E711" s="2">
+        <v>115</v>
+      </c>
+      <c r="F711" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G711" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H711" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I711" s="2"/>
+      <c r="J711" s="2"/>
+      <c r="K711" s="2"/>
+    </row>
+    <row r="712" spans="1:11" ht="30">
+      <c r="A712" s="4">
+        <v>331</v>
+      </c>
+      <c r="B712" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C712" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D712" s="2">
+        <v>435</v>
+      </c>
+      <c r="E712" s="2">
+        <v>270</v>
+      </c>
+      <c r="F712" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G712" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H712" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I712" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J712" s="2"/>
+      <c r="K712" s="2"/>
+    </row>
+    <row r="713" spans="1:11" ht="30">
+      <c r="A713" s="4">
+        <v>331</v>
+      </c>
+      <c r="B713" s="2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C713" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D713" s="2"/>
+      <c r="E713" s="2">
+        <v>11.52</v>
+      </c>
+      <c r="F713" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G713" s="2"/>
+      <c r="H713" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I713" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J713" s="2"/>
+      <c r="K713" s="2"/>
+    </row>
+    <row r="714" spans="1:11" ht="30">
+      <c r="A714" s="4">
+        <v>331</v>
+      </c>
+      <c r="B714" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C714" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D714" s="2"/>
+      <c r="E714" s="2">
+        <v>239.5</v>
+      </c>
+      <c r="F714" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G714" s="2"/>
+      <c r="H714" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I714" s="2"/>
+      <c r="J714" s="2"/>
+      <c r="K714" s="2"/>
+    </row>
+    <row r="715" spans="1:11" ht="30">
+      <c r="A715" s="4">
+        <v>331</v>
+      </c>
+      <c r="B715" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C715" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D715" s="2">
+        <v>153</v>
+      </c>
+      <c r="E715" s="2">
+        <v>152</v>
+      </c>
+      <c r="F715" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G715" s="2"/>
+      <c r="H715" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I715" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J715" s="2"/>
+      <c r="K715" s="2"/>
+    </row>
+    <row r="716" spans="1:11" ht="30">
+      <c r="A716" s="4">
+        <v>332</v>
+      </c>
+      <c r="B716" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C716" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D716" s="2">
+        <v>698</v>
+      </c>
+      <c r="E716" s="2">
+        <v>447</v>
+      </c>
+      <c r="F716" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G716" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H716" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I716" s="2"/>
+      <c r="J716" s="2"/>
+      <c r="K716" s="2"/>
+    </row>
+    <row r="717" spans="1:11" ht="30">
+      <c r="A717" s="4">
+        <v>333</v>
+      </c>
+      <c r="B717" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C717" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D717" s="2"/>
+      <c r="E717" s="2">
+        <v>27.53</v>
+      </c>
+      <c r="F717" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G717" s="2"/>
+      <c r="H717" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I717" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J717" s="2"/>
+      <c r="K717" s="2"/>
+    </row>
+    <row r="718" spans="1:11" ht="30">
+      <c r="A718" s="4">
+        <v>333</v>
+      </c>
+      <c r="B718" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C718" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D718" s="2"/>
+      <c r="E718" s="2">
+        <v>292</v>
+      </c>
+      <c r="F718" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G718" s="2"/>
+      <c r="H718" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I718" s="2"/>
+      <c r="J718" s="2"/>
+      <c r="K718" s="2"/>
+    </row>
+    <row r="719" spans="1:11" ht="15">
+      <c r="A719" s="4">
+        <v>334</v>
+      </c>
+      <c r="B719" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C719" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D719" s="2">
+        <v>189</v>
+      </c>
+      <c r="E719" s="2">
+        <v>141</v>
+      </c>
+      <c r="F719" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G719" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="H719" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I719" s="2"/>
+      <c r="J719" s="2"/>
+      <c r="K719" s="2"/>
+    </row>
+    <row r="720" spans="1:11" ht="15">
+      <c r="A720" s="4">
+        <v>335</v>
+      </c>
+      <c r="B720" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C720" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D720" s="2"/>
+      <c r="E720" s="2">
+        <v>115</v>
+      </c>
+      <c r="F720" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G720" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H720" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I720" s="2"/>
+      <c r="J720" s="2"/>
+      <c r="K720" s="2"/>
+    </row>
+    <row r="721" spans="1:11" ht="15">
+      <c r="A721" s="4">
+        <v>335</v>
+      </c>
+      <c r="B721" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C721" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D721" s="2">
+        <v>115</v>
+      </c>
+      <c r="E721" s="2">
+        <v>99.5</v>
+      </c>
+      <c r="F721" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G721" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H721" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I721" s="2"/>
+      <c r="J721" s="2"/>
+      <c r="K721" s="2"/>
+    </row>
+    <row r="722" spans="1:11" ht="30">
+      <c r="A722" s="4">
+        <v>336</v>
+      </c>
+      <c r="B722" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C722" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D722" s="2"/>
+      <c r="E722" s="2">
+        <v>599</v>
+      </c>
+      <c r="F722" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G722" s="2"/>
+      <c r="H722" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I722" s="2"/>
+      <c r="J722" s="2"/>
+      <c r="K722" s="2"/>
+    </row>
+    <row r="723" spans="1:11" ht="30">
+      <c r="A723" s="4">
+        <v>336</v>
+      </c>
+      <c r="B723" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C723" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D723" s="2">
+        <v>980</v>
+      </c>
+      <c r="E723" s="2">
+        <v>607.6</v>
+      </c>
+      <c r="F723" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G723" s="2"/>
+      <c r="H723" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I723" s="2"/>
+      <c r="J723" s="2"/>
+      <c r="K723" s="2"/>
+    </row>
+    <row r="724" spans="1:11" ht="30">
+      <c r="A724" s="4">
+        <v>336</v>
+      </c>
+      <c r="B724" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C724" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D724" s="2"/>
+      <c r="E724" s="2">
+        <v>559</v>
+      </c>
+      <c r="F724" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G724" s="2"/>
+      <c r="H724" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I724" s="2"/>
+      <c r="J724" s="2"/>
+      <c r="K724" s="2"/>
+    </row>
+    <row r="725" spans="1:11" ht="30">
+      <c r="A725" s="4">
+        <v>337</v>
+      </c>
+      <c r="B725" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C725" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D725" s="2"/>
+      <c r="E725" s="2">
+        <v>550</v>
+      </c>
+      <c r="F725" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G725" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H725" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I725" s="2"/>
+      <c r="J725" s="2"/>
+      <c r="K725" s="2"/>
+    </row>
+    <row r="726" spans="1:11" ht="30">
+      <c r="A726" s="4">
+        <v>338</v>
+      </c>
+      <c r="B726" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C726" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D726" s="2">
+        <v>568</v>
+      </c>
+      <c r="E726" s="2">
+        <v>425</v>
+      </c>
+      <c r="F726" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G726" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="H726" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I726" s="2"/>
+      <c r="J726" s="2"/>
+      <c r="K726" s="2"/>
+    </row>
+    <row r="727" spans="1:11" ht="30">
+      <c r="A727" s="4">
+        <v>339</v>
+      </c>
+      <c r="B727" s="2" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C727" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D727" s="2">
+        <v>420</v>
+      </c>
+      <c r="E727" s="2">
+        <v>336</v>
+      </c>
+      <c r="F727" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G727" s="2"/>
+      <c r="H727" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I727" s="2"/>
+      <c r="J727" s="2"/>
+      <c r="K727" s="2"/>
+    </row>
+    <row r="728" spans="1:11" ht="30">
+      <c r="A728" s="4">
+        <v>340</v>
+      </c>
+      <c r="B728" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C728" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D728" s="2"/>
+      <c r="E728" s="2">
+        <v>500</v>
+      </c>
+      <c r="F728" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G728" s="2"/>
+      <c r="H728" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I728" s="2"/>
+      <c r="J728" s="2"/>
+      <c r="K728" s="2"/>
+    </row>
+    <row r="729" spans="1:11" ht="30">
+      <c r="A729" s="4">
+        <v>340</v>
+      </c>
+      <c r="B729" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C729" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D729" s="2"/>
+      <c r="E729" s="2">
+        <v>298</v>
+      </c>
+      <c r="F729" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G729" s="2"/>
+      <c r="H729" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I729" s="2"/>
+      <c r="J729" s="2"/>
+      <c r="K729" s="2"/>
+    </row>
+    <row r="730" spans="1:11" ht="30">
+      <c r="A730" s="4">
+        <v>340</v>
+      </c>
+      <c r="B730" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C730" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D730" s="2">
+        <v>319</v>
+      </c>
+      <c r="E730" s="2">
+        <v>312.64</v>
+      </c>
+      <c r="F730" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G730" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H730" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I730" s="2"/>
+      <c r="J730" s="2"/>
+      <c r="K730" s="2"/>
+    </row>
+    <row r="731" spans="1:11" ht="30">
+      <c r="A731" s="4">
+        <v>341</v>
+      </c>
+      <c r="B731" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C731" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D731" s="2"/>
+      <c r="E731" s="2">
+        <v>298</v>
+      </c>
+      <c r="F731" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G731" s="2"/>
+      <c r="H731" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I731" s="2"/>
+      <c r="J731" s="2"/>
+      <c r="K731" s="2"/>
+    </row>
+    <row r="732" spans="1:11" ht="30">
+      <c r="A732" s="4">
+        <v>341</v>
+      </c>
+      <c r="B732" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C732" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D732" s="2"/>
+      <c r="E732" s="2">
+        <v>298</v>
+      </c>
+      <c r="F732" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G732" s="2"/>
+      <c r="H732" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I732" s="2"/>
+      <c r="J732" s="2"/>
+      <c r="K732" s="2"/>
+    </row>
+    <row r="733" spans="1:11" ht="30">
+      <c r="A733" s="4">
+        <v>341</v>
+      </c>
+      <c r="B733" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C733" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D733" s="2"/>
+      <c r="E733" s="2">
+        <v>298</v>
+      </c>
+      <c r="F733" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G733" s="2"/>
+      <c r="H733" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I733" s="2"/>
+      <c r="J733" s="2"/>
+      <c r="K733" s="2"/>
+    </row>
+    <row r="734" spans="1:11" ht="15">
+      <c r="A734" s="4">
+        <v>342</v>
+      </c>
+      <c r="B734" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C734" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D734" s="2">
+        <v>1050</v>
+      </c>
+      <c r="E734" s="2">
+        <v>907</v>
+      </c>
+      <c r="F734" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G734" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H734" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I734" s="2"/>
+      <c r="J734" s="2"/>
+      <c r="K734" s="2"/>
+    </row>
+    <row r="735" spans="1:11" ht="15">
+      <c r="A735" s="4">
+        <v>343</v>
+      </c>
+      <c r="B735" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C735" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D735" s="2"/>
+      <c r="E735" s="2">
+        <v>209</v>
+      </c>
+      <c r="F735" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G735" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H735" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I735" s="2"/>
+      <c r="J735" s="2"/>
+      <c r="K735" s="2"/>
+    </row>
+    <row r="736" spans="1:11" ht="15">
+      <c r="A736" s="4">
+        <v>344</v>
+      </c>
+      <c r="B736" s="2" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C736" s="2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D736" s="2">
+        <v>259</v>
+      </c>
+      <c r="E736" s="2">
+        <v>188</v>
+      </c>
+      <c r="F736" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G736" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H736" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I736" s="2"/>
+      <c r="J736" s="2"/>
+      <c r="K736" s="2"/>
+    </row>
+    <row r="737" spans="1:11" ht="30">
+      <c r="A737" s="4">
+        <v>345</v>
+      </c>
+      <c r="B737" s="2" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C737" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D737" s="2"/>
+      <c r="E737" s="2">
+        <v>106</v>
+      </c>
+      <c r="F737" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G737" s="2"/>
+      <c r="H737" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I737" s="2"/>
+      <c r="J737" s="2"/>
+      <c r="K737" s="2"/>
+    </row>
+    <row r="738" spans="1:11" ht="15">
+      <c r="A738" s="4">
+        <v>345</v>
+      </c>
+      <c r="B738" s="2" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C738" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D738" s="2">
+        <v>169</v>
+      </c>
+      <c r="E738" s="2">
+        <v>145</v>
+      </c>
+      <c r="F738" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G738" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="H738" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I738" s="2"/>
+      <c r="J738" s="2"/>
+      <c r="K738" s="2"/>
+    </row>
+    <row r="739" spans="1:11" ht="15">
+      <c r="A739" s="4">
+        <v>345</v>
+      </c>
+      <c r="B739" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C739" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D739" s="2"/>
+      <c r="E739" s="2">
+        <v>122</v>
+      </c>
+      <c r="F739" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G739" s="2"/>
+      <c r="H739" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I739" s="2"/>
+      <c r="J739" s="2"/>
+      <c r="K739" s="2"/>
+    </row>
+    <row r="740" spans="1:11" ht="30">
+      <c r="A740" s="4">
+        <v>345</v>
+      </c>
+      <c r="B740" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C740" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D740" s="2"/>
+      <c r="E740" s="2">
+        <v>169</v>
+      </c>
+      <c r="F740" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G740" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H740" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I740" s="2"/>
+      <c r="J740" s="2"/>
+      <c r="K740" s="2"/>
+    </row>
+    <row r="741" spans="1:11" ht="30">
+      <c r="A741" s="4">
+        <v>346</v>
+      </c>
+      <c r="B741" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="C741" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D741" s="2">
+        <v>199</v>
+      </c>
+      <c r="E741" s="2">
+        <v>120.8</v>
+      </c>
+      <c r="F741" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G741" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="H741" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I741" s="2"/>
+      <c r="J741" s="2"/>
+      <c r="K741" s="2"/>
+    </row>
+    <row r="742" spans="1:11" ht="30">
+      <c r="A742" s="4">
+        <v>347</v>
+      </c>
+      <c r="B742" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C742" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D742" s="2">
+        <v>899</v>
+      </c>
+      <c r="E742" s="2">
+        <v>715</v>
+      </c>
+      <c r="F742" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G742" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H742" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I742" s="2"/>
+      <c r="J742" s="2"/>
+      <c r="K742" s="2"/>
+    </row>
+    <row r="743" spans="1:11" ht="30">
+      <c r="A743" s="4">
+        <v>348</v>
+      </c>
+      <c r="B743" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C743" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D743" s="2"/>
+      <c r="E743" s="2">
+        <v>119</v>
+      </c>
+      <c r="F743" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G743" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="H743" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I743" s="2"/>
+      <c r="J743" s="2"/>
+      <c r="K743" s="2"/>
+    </row>
+    <row r="744" spans="1:11" ht="30">
+      <c r="A744" s="4">
+        <v>348</v>
+      </c>
+      <c r="B744" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C744" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D744" s="2">
+        <v>113</v>
+      </c>
+      <c r="E744" s="2">
+        <v>127</v>
+      </c>
+      <c r="F744" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G744" s="2" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H744" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I744" s="2"/>
+      <c r="J744" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="K744" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="745" spans="1:11" ht="30">
+      <c r="A745" s="4">
+        <v>348</v>
+      </c>
+      <c r="B745" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C745" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D745" s="2"/>
+      <c r="E745" s="2">
+        <v>115</v>
+      </c>
+      <c r="F745" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G745" s="2" t="s">
+        <v>1267</v>
+      </c>
+      <c r="H745" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I745" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="J745" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K745" s="2"/>
+    </row>
+    <row r="746" spans="1:11" ht="30">
+      <c r="A746" s="4">
+        <v>348</v>
+      </c>
+      <c r="B746" s="2" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C746" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D746" s="2"/>
+      <c r="E746" s="2">
+        <v>164</v>
+      </c>
+      <c r="F746" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G746" s="2" t="s">
+        <v>1271</v>
+      </c>
+      <c r="H746" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I746" s="2"/>
+      <c r="J746" s="2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="K746" s="2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="747" spans="1:11" ht="30">
+      <c r="A747" s="4">
+        <v>349</v>
+      </c>
+      <c r="B747" s="2" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C747" s="2" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D747" s="2"/>
+      <c r="E747" s="2">
+        <v>112.6</v>
+      </c>
+      <c r="F747" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G747" s="2"/>
+      <c r="H747" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I747" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="J747" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K747" s="2"/>
+    </row>
+    <row r="748" spans="1:11" ht="30">
+      <c r="A748" s="4">
+        <v>349</v>
+      </c>
+      <c r="B748" s="2" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C748" s="2" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D748" s="2">
+        <v>149</v>
+      </c>
+      <c r="E748" s="2">
+        <v>147</v>
+      </c>
+      <c r="F748" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G748" s="2" t="s">
+        <v>1276</v>
+      </c>
+      <c r="H748" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I748" s="2"/>
+      <c r="J748" s="2"/>
+      <c r="K748" s="2"/>
+    </row>
+    <row r="749" spans="1:11" ht="30">
+      <c r="A749" s="4">
+        <v>349</v>
+      </c>
+      <c r="B749" s="2" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C749" s="2" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D749" s="2"/>
+      <c r="E749" s="2">
+        <v>130</v>
+      </c>
+      <c r="F749" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G749" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H749" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I749" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="J749" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K749" s="2"/>
+    </row>
+    <row r="750" spans="1:11" ht="30">
+      <c r="A750" s="4">
+        <v>350</v>
+      </c>
+      <c r="B750" s="2" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C750" s="2" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D750" s="2">
+        <v>699</v>
+      </c>
+      <c r="E750" s="2">
+        <v>439</v>
+      </c>
+      <c r="F750" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G750" s="2"/>
+      <c r="H750" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I750" s="2"/>
+      <c r="J750" s="2"/>
+      <c r="K750" s="2"/>
+    </row>
+    <row r="751" spans="1:11" ht="30">
+      <c r="A751" s="4">
+        <v>350</v>
+      </c>
+      <c r="B751" s="2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C751" s="2" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D751" s="2"/>
+      <c r="E751" s="2">
+        <v>445</v>
+      </c>
+      <c r="F751" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G751" s="2"/>
+      <c r="H751" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I751" s="2"/>
+      <c r="J751" s="2"/>
+      <c r="K751" s="2"/>
+    </row>
+    <row r="752" spans="1:11" ht="30">
+      <c r="A752" s="4">
+        <v>350</v>
+      </c>
+      <c r="B752" s="2" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C752" s="2" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D752" s="2"/>
+      <c r="E752" s="2">
+        <v>298</v>
+      </c>
+      <c r="F752" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G752" s="2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H752" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I752" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="J752" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K752" s="2"/>
+    </row>
+    <row r="753" spans="1:11" ht="30">
+      <c r="A753" s="4">
+        <v>351</v>
+      </c>
+      <c r="B753" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C753" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D753" s="2"/>
+      <c r="E753" s="2">
+        <v>125</v>
+      </c>
+      <c r="F753" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G753" s="2"/>
+      <c r="H753" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I753" s="2"/>
+      <c r="J753" s="2"/>
+      <c r="K753" s="2"/>
+    </row>
+    <row r="754" spans="1:11" ht="30">
+      <c r="A754" s="4">
+        <v>351</v>
+      </c>
+      <c r="B754" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C754" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D754" s="2"/>
+      <c r="E754" s="2">
+        <v>125</v>
+      </c>
+      <c r="F754" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G754" s="2"/>
+      <c r="H754" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I754" s="2"/>
+      <c r="J754" s="2"/>
+      <c r="K754" s="2"/>
+    </row>
+    <row r="755" spans="1:11" ht="15">
+      <c r="A755" s="4">
+        <v>352</v>
+      </c>
+      <c r="B755" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C755" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D755" s="2">
+        <v>2691</v>
+      </c>
+      <c r="E755" s="2">
+        <v>269</v>
+      </c>
+      <c r="F755" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G755" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="H755" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I755" s="2"/>
+      <c r="J755" s="2"/>
+      <c r="K755" s="2"/>
+    </row>
+    <row r="756" spans="1:11" ht="15">
+      <c r="A756" s="4">
+        <v>352</v>
+      </c>
+      <c r="B756" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C756" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D756" s="2"/>
+      <c r="E756" s="2">
+        <v>269</v>
+      </c>
+      <c r="F756" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G756" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H756" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I756" s="2"/>
+      <c r="J756" s="2"/>
+      <c r="K756" s="2"/>
+    </row>
+    <row r="757" spans="1:11" ht="15">
+      <c r="A757" s="4">
+        <v>352</v>
+      </c>
+      <c r="B757" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C757" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D757" s="2"/>
+      <c r="E757" s="2">
+        <v>517</v>
+      </c>
+      <c r="F757" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G757" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H757" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I757" s="2"/>
+      <c r="J757" s="2"/>
+      <c r="K757" s="2"/>
+    </row>
+    <row r="758" spans="1:11" ht="30">
+      <c r="A758" s="4">
+        <v>353</v>
+      </c>
+      <c r="B758" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C758" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D758" s="2">
+        <v>999</v>
+      </c>
+      <c r="E758" s="2">
+        <v>747</v>
+      </c>
+      <c r="F758" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G758" s="2" t="s">
+        <v>1292</v>
+      </c>
+      <c r="H758" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I758" s="2"/>
+      <c r="J758" s="2"/>
+      <c r="K758" s="2"/>
+    </row>
+    <row r="759" spans="1:11" ht="15">
+      <c r="A759" s="4">
+        <v>353</v>
+      </c>
+      <c r="B759" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C759" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D759" s="2">
+        <v>899</v>
+      </c>
+      <c r="E759" s="2">
+        <v>715</v>
+      </c>
+      <c r="F759" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G759" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H759" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I759" s="2"/>
+      <c r="J759" s="2"/>
+      <c r="K759" s="2"/>
+    </row>
+    <row r="760" spans="1:11" ht="30">
+      <c r="A760" s="4">
+        <v>354</v>
+      </c>
+      <c r="B760" s="2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C760" s="2" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D760" s="2">
+        <v>84.9</v>
+      </c>
+      <c r="E760" s="2">
+        <v>61</v>
+      </c>
+      <c r="F760" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G760" s="2"/>
+      <c r="H760" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I760" s="2"/>
+      <c r="J760" s="2"/>
+      <c r="K760" s="2"/>
+    </row>
+    <row r="761" spans="1:11" ht="30">
+      <c r="A761" s="4">
+        <v>355</v>
+      </c>
+      <c r="B761" s="2" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C761" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D761" s="2"/>
+      <c r="E761" s="2">
+        <v>128</v>
+      </c>
+      <c r="F761" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G761" s="2"/>
+      <c r="H761" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I761" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="J761" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K761" s="2"/>
+    </row>
+    <row r="762" spans="1:11" ht="30">
+      <c r="A762" s="4">
+        <v>355</v>
+      </c>
+      <c r="B762" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C762" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D762" s="2"/>
+      <c r="E762" s="2">
+        <v>367</v>
+      </c>
+      <c r="F762" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G762" s="2" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H762" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I762" s="2"/>
+      <c r="J762" s="2" t="s">
+        <v>1299</v>
+      </c>
+      <c r="K762" s="2">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="763" spans="1:11" ht="30">
+      <c r="A763" s="4">
+        <v>355</v>
+      </c>
+      <c r="B763" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C763" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D763" s="2"/>
+      <c r="E763" s="2">
+        <v>128</v>
+      </c>
+      <c r="F763" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G763" s="2"/>
+      <c r="H763" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I763" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="J763" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K763" s="2"/>
+    </row>
+    <row r="764" spans="1:11" ht="30">
+      <c r="A764" s="4">
+        <v>356</v>
+      </c>
+      <c r="B764" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C764" s="2" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D764" s="2">
+        <v>235</v>
+      </c>
+      <c r="E764" s="2">
+        <v>143.4</v>
+      </c>
+      <c r="F764" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G764" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H764" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I764" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="J764" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K764" s="2"/>
+    </row>
+    <row r="765" spans="1:11" ht="45">
+      <c r="A765" s="4">
+        <v>356</v>
+      </c>
+      <c r="B765" s="2" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C765" s="2" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D765" s="2"/>
+      <c r="E765" s="2">
+        <v>59.9</v>
+      </c>
+      <c r="F765" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G765" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H765" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I765" s="2" t="s">
+        <v>1303</v>
+      </c>
+      <c r="J765" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K765" s="2"/>
+    </row>
+    <row r="766" spans="1:11" ht="30">
+      <c r="A766" s="4">
+        <v>356</v>
+      </c>
+      <c r="B766" s="2" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C766" s="2" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D766" s="2"/>
+      <c r="E766" s="2">
+        <v>128</v>
+      </c>
+      <c r="F766" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G766" s="2"/>
+      <c r="H766" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I766" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="J766" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K766" s="2"/>
+    </row>
+    <row r="767" spans="1:11" ht="15">
+      <c r="A767" s="4">
+        <v>356</v>
+      </c>
+      <c r="B767" s="2" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C767" s="2" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D767" s="2">
+        <v>410</v>
+      </c>
+      <c r="E767" s="2">
+        <v>295.2</v>
+      </c>
+      <c r="F767" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G767" s="2"/>
+      <c r="H767" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I767" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="J767" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K767" s="2"/>
+    </row>
+    <row r="768" spans="1:11" ht="30">
+      <c r="A768" s="4">
+        <v>356</v>
+      </c>
+      <c r="B768" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C768" s="2" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D768" s="2"/>
+      <c r="E768" s="2">
+        <v>128</v>
+      </c>
+      <c r="F768" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G768" s="2"/>
+      <c r="H768" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I768" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="J768" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K768" s="2"/>
+    </row>
+    <row r="769" spans="1:11" ht="30">
+      <c r="A769" s="4">
+        <v>357</v>
+      </c>
+      <c r="B769" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C769" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D769" s="2">
+        <v>235</v>
+      </c>
+      <c r="E769" s="2">
+        <v>143.4</v>
+      </c>
+      <c r="F769" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G769" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H769" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I769" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="J769" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K769" s="2"/>
+    </row>
+    <row r="770" spans="1:11" ht="30">
+      <c r="A770" s="4">
+        <v>357</v>
+      </c>
+      <c r="B770" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C770" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D770" s="2">
+        <v>245</v>
+      </c>
+      <c r="E770" s="2">
+        <v>146.19999999999999</v>
+      </c>
+      <c r="F770" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G770" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H770" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I770" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="J770" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K770" s="2"/>
+    </row>
+    <row r="771" spans="1:11" ht="45">
+      <c r="A771" s="4">
+        <v>357</v>
+      </c>
+      <c r="B771" s="2" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C771" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D771" s="2">
+        <v>280</v>
+      </c>
+      <c r="E771" s="2">
+        <v>170.8</v>
+      </c>
+      <c r="F771" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G771" s="2" t="s">
+        <v>1309</v>
+      </c>
+      <c r="H771" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I771" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="J771" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K771" s="2"/>
+    </row>
+    <row r="772" spans="1:11" ht="30">
+      <c r="A772" s="4">
+        <v>357</v>
+      </c>
+      <c r="B772" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C772" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D772" s="2">
+        <v>195</v>
+      </c>
+      <c r="E772" s="2">
+        <v>119</v>
+      </c>
+      <c r="F772" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G772" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="H772" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I772" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="J772" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K772" s="2"/>
+    </row>
+    <row r="773" spans="1:11" ht="30">
+      <c r="A773" s="4">
+        <v>357</v>
+      </c>
+      <c r="B773" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C773" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D773" s="2"/>
+      <c r="E773" s="2">
+        <v>158</v>
+      </c>
+      <c r="F773" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G773" s="2"/>
+      <c r="H773" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I773" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="J773" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K773" s="2"/>
+    </row>
+    <row r="774" spans="1:11" ht="30">
+      <c r="A774" s="4">
+        <v>357</v>
+      </c>
+      <c r="B774" s="2" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C774" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D774" s="2"/>
+      <c r="E774" s="2">
+        <v>158</v>
+      </c>
+      <c r="F774" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G774" s="2"/>
+      <c r="H774" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I774" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="J774" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K774" s="2"/>
+    </row>
+    <row r="775" spans="1:11" ht="30">
+      <c r="A775" s="4">
+        <v>357</v>
+      </c>
+      <c r="B775" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C775" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D775" s="2"/>
+      <c r="E775" s="2">
+        <v>118</v>
+      </c>
+      <c r="F775" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G775" s="2"/>
+      <c r="H775" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I775" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="J775" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K775" s="2"/>
+    </row>
+    <row r="776" spans="1:11" ht="30">
+      <c r="A776" s="4">
+        <v>358</v>
+      </c>
+      <c r="B776" s="2" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C776" s="2" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D776" s="2">
+        <v>183.7</v>
+      </c>
+      <c r="E776" s="2">
+        <v>112.1</v>
+      </c>
+      <c r="F776" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G776" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="H776" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I776" s="2"/>
+      <c r="J776" s="2" t="s">
+        <v>1318</v>
+      </c>
+      <c r="K776" s="2">
+        <v>112.1</v>
+      </c>
+    </row>
+    <row r="777" spans="1:11" ht="15">
+      <c r="A777" s="4">
+        <v>359</v>
+      </c>
+      <c r="B777" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C777" s="2" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D777" s="2">
+        <v>121.3</v>
+      </c>
+      <c r="E777" s="2">
+        <v>77.5</v>
+      </c>
+      <c r="F777" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G777" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H777" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I777" s="2"/>
+      <c r="J777" s="2"/>
+      <c r="K777" s="2"/>
+    </row>
+    <row r="778" spans="1:11" ht="30">
+      <c r="A778" s="4">
+        <v>359</v>
+      </c>
+      <c r="B778" s="2" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C778" s="2" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D778" s="2">
+        <v>124.2</v>
+      </c>
+      <c r="E778" s="2">
+        <v>84.5</v>
+      </c>
+      <c r="F778" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G778" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="H778" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I778" s="2"/>
+      <c r="J778" s="2" t="s">
+        <v>1322</v>
+      </c>
+      <c r="K778" s="2">
+        <v>84.5</v>
+      </c>
+    </row>
+    <row r="779" spans="1:11" ht="30">
+      <c r="A779" s="4">
+        <v>359</v>
+      </c>
+      <c r="B779" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C779" s="2" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D779" s="2">
+        <v>280</v>
+      </c>
+      <c r="E779" s="2">
+        <v>148</v>
+      </c>
+      <c r="F779" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G779" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="H779" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I779" s="2"/>
+      <c r="J779" s="2"/>
+      <c r="K779" s="2"/>
+    </row>
+    <row r="780" spans="1:11" ht="30">
+      <c r="A780" s="4">
+        <v>360</v>
+      </c>
+      <c r="B780" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C780" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D780" s="2">
+        <v>1299</v>
+      </c>
+      <c r="E780" s="2">
+        <v>999</v>
+      </c>
+      <c r="F780" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G780" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="H780" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I780" s="2"/>
+      <c r="J780" s="2"/>
+      <c r="K780" s="2"/>
+    </row>
+    <row r="781" spans="1:11" ht="15">
+      <c r="A781" s="4">
+        <v>361</v>
+      </c>
+      <c r="B781" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C781" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D781" s="2">
+        <v>868</v>
+      </c>
+      <c r="E781" s="2">
+        <v>607</v>
+      </c>
+      <c r="F781" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G781" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H781" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I781" s="2"/>
+      <c r="J781" s="2"/>
+      <c r="K781" s="2"/>
+    </row>
+    <row r="782" spans="1:11" ht="15">
+      <c r="A782" s="4">
+        <v>362</v>
+      </c>
+      <c r="B782" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C782" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="D782" s="2">
+        <v>879</v>
+      </c>
+      <c r="E782" s="2">
+        <v>698</v>
+      </c>
+      <c r="F782" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G782" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="H782" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I782" s="2"/>
+      <c r="J782" s="2"/>
+      <c r="K782" s="2"/>
+    </row>
+    <row r="783" spans="1:11" ht="15">
+      <c r="A783" s="4">
+        <v>362</v>
+      </c>
+      <c r="B783" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C783" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="D783" s="2">
+        <v>870</v>
+      </c>
+      <c r="E783" s="2">
+        <v>643</v>
+      </c>
+      <c r="F783" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G783" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="H783" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I783" s="2"/>
+      <c r="J783" s="2"/>
+      <c r="K783" s="2"/>
+    </row>
+    <row r="784" spans="1:11" ht="15">
+      <c r="A784" s="4">
+        <v>362</v>
+      </c>
+      <c r="B784" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C784" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="D784" s="2">
+        <v>868</v>
+      </c>
+      <c r="E784" s="2">
+        <v>607</v>
+      </c>
+      <c r="F784" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G784" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H784" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I784" s="2"/>
+      <c r="J784" s="2"/>
+      <c r="K784" s="2"/>
+    </row>
+    <row r="785" spans="1:11" ht="30">
+      <c r="A785" s="4">
+        <v>363</v>
+      </c>
+      <c r="B785" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C785" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D785" s="2">
+        <v>234</v>
+      </c>
+      <c r="E785" s="2">
+        <v>143.15</v>
+      </c>
+      <c r="F785" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G785" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="H785" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I785" s="2"/>
+      <c r="J785" s="2"/>
+      <c r="K785" s="2"/>
+    </row>
+    <row r="786" spans="1:11" ht="30">
+      <c r="A786" s="4">
+        <v>363</v>
+      </c>
+      <c r="B786" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C786" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D786" s="2">
+        <v>259</v>
+      </c>
+      <c r="E786" s="2">
+        <v>158.84</v>
+      </c>
+      <c r="F786" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G786" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="H786" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I786" s="2"/>
+      <c r="J786" s="2"/>
+      <c r="K786" s="2"/>
+    </row>
+    <row r="787" spans="1:11" ht="30">
+      <c r="A787" s="4">
+        <v>364</v>
+      </c>
+      <c r="B787" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C787" s="2" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D787" s="2">
+        <v>1300</v>
+      </c>
+      <c r="E787" s="2">
+        <v>782</v>
+      </c>
+      <c r="F787" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G787" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H787" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I787" s="2"/>
+      <c r="J787" s="2"/>
+      <c r="K787" s="2"/>
+    </row>
+    <row r="788" spans="1:11" ht="30">
+      <c r="A788" s="4">
+        <v>364</v>
+      </c>
+      <c r="B788" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C788" s="2" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D788" s="2">
+        <v>1218</v>
+      </c>
+      <c r="E788" s="2">
+        <v>775</v>
+      </c>
+      <c r="F788" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G788" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H788" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I788" s="2"/>
+      <c r="J788" s="2"/>
+      <c r="K788" s="2"/>
+    </row>
+    <row r="789" spans="1:11" ht="30">
+      <c r="A789" s="4">
+        <v>365</v>
+      </c>
+      <c r="B789" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="C789" s="2" t="s">
+        <v>1331</v>
+      </c>
+      <c r="D789" s="2">
+        <v>253</v>
+      </c>
+      <c r="E789" s="2">
+        <v>198</v>
+      </c>
+      <c r="F789" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G789" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H789" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I789" s="2"/>
+      <c r="J789" s="2"/>
+      <c r="K789" s="2"/>
+    </row>
+    <row r="790" spans="1:11" ht="15">
+      <c r="A790" s="4">
+        <v>365</v>
+      </c>
+      <c r="B790" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="C790" s="2" t="s">
+        <v>1331</v>
+      </c>
+      <c r="D790" s="2">
+        <v>289</v>
+      </c>
+      <c r="E790" s="2">
+        <v>170</v>
+      </c>
+      <c r="F790" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G790" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="H790" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I790" s="2"/>
+      <c r="J790" s="2"/>
+      <c r="K790" s="2"/>
+    </row>
+    <row r="791" spans="1:11" ht="15">
+      <c r="A791" s="4">
+        <v>365</v>
+      </c>
+      <c r="B791" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="C791" s="2" t="s">
+        <v>1331</v>
+      </c>
+      <c r="D791" s="2">
+        <v>269</v>
+      </c>
+      <c r="E791" s="2">
+        <v>161.80000000000001</v>
+      </c>
+      <c r="F791" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G791" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="H791" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I791" s="2"/>
+      <c r="J791" s="2"/>
+      <c r="K791" s="2"/>
+    </row>
+    <row r="792" spans="1:11" ht="15">
+      <c r="A792" s="4">
+        <v>366</v>
+      </c>
+      <c r="B792" s="2" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C792" s="2" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D792" s="2"/>
+      <c r="E792" s="2">
+        <v>305</v>
+      </c>
+      <c r="F792" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G792" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="H792" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I792" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="J792" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K792" s="2"/>
+    </row>
+    <row r="793" spans="1:11" ht="30">
+      <c r="A793" s="4">
+        <v>367</v>
+      </c>
+      <c r="B793" s="2" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C793" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D793" s="2">
+        <v>1060</v>
+      </c>
+      <c r="E793" s="2">
+        <v>879.8</v>
+      </c>
+      <c r="F793" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G793" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H793" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I793" s="2"/>
+      <c r="J793" s="2"/>
+      <c r="K793" s="2"/>
+    </row>
+    <row r="794" spans="1:11" ht="30">
+      <c r="A794" s="4">
+        <v>367</v>
+      </c>
+      <c r="B794" s="2" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C794" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D794" s="2">
+        <v>459</v>
+      </c>
+      <c r="E794" s="2">
+        <v>649</v>
+      </c>
+      <c r="F794" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G794" s="2"/>
+      <c r="H794" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I794" s="2"/>
+      <c r="J794" s="2" t="s">
+        <v>1338</v>
+      </c>
+      <c r="K794" s="2">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="795" spans="1:11" ht="30">
+      <c r="A795" s="4">
+        <v>367</v>
+      </c>
+      <c r="B795" s="2" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C795" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D795" s="2"/>
+      <c r="E795" s="2">
+        <v>768</v>
+      </c>
+      <c r="F795" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G795" s="2"/>
+      <c r="H795" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I795" s="2"/>
+      <c r="J795" s="2" t="s">
+        <v>1338</v>
+      </c>
+      <c r="K795" s="2">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="796" spans="1:11" ht="30">
+      <c r="A796" s="4">
+        <v>368</v>
+      </c>
+      <c r="B796" s="2" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C796" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D796" s="2"/>
+      <c r="E796" s="2">
+        <v>768</v>
+      </c>
+      <c r="F796" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G796" s="2"/>
+      <c r="H796" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I796" s="2"/>
+      <c r="J796" s="2" t="s">
+        <v>1342</v>
+      </c>
+      <c r="K796" s="2">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="797" spans="1:11" ht="15">
+      <c r="A797" s="4">
+        <v>368</v>
+      </c>
+      <c r="B797" s="2" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C797" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D797" s="2">
+        <v>299.89999999999998</v>
+      </c>
+      <c r="E797" s="2">
+        <v>296</v>
+      </c>
+      <c r="F797" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G797" s="2"/>
+      <c r="H797" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I797" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="J797" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K797" s="2"/>
+    </row>
+    <row r="798" spans="1:11" ht="30">
+      <c r="A798" s="4">
+        <v>368</v>
+      </c>
+      <c r="B798" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C798" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D798" s="2"/>
+      <c r="E798" s="2">
+        <v>697</v>
+      </c>
+      <c r="F798" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G798" s="2"/>
+      <c r="H798" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I798" s="2"/>
+      <c r="J798" s="2" t="s">
+        <v>1338</v>
+      </c>
+      <c r="K798" s="2">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="799" spans="1:11" ht="30">
+      <c r="A799" s="4">
+        <v>369</v>
+      </c>
+      <c r="B799" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="C799" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D799" s="2">
+        <v>449</v>
+      </c>
+      <c r="E799" s="2">
+        <v>398</v>
+      </c>
+      <c r="F799" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G799" s="2"/>
+      <c r="H799" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I799" s="2"/>
+      <c r="J799" s="2"/>
+      <c r="K799" s="2"/>
+    </row>
+    <row r="800" spans="1:11" ht="30">
+      <c r="A800" s="4">
+        <v>370</v>
+      </c>
+      <c r="B800" s="2" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C800" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D800" s="2">
+        <v>789</v>
+      </c>
+      <c r="E800" s="2">
+        <v>508.8</v>
+      </c>
+      <c r="F800" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G800" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="H800" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I800" s="2"/>
+      <c r="J800" s="2"/>
+      <c r="K800" s="2"/>
+    </row>
+    <row r="801" spans="1:11" ht="15">
+      <c r="A801" s="4">
+        <v>370</v>
+      </c>
+      <c r="B801" s="2" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C801" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D801" s="2">
+        <v>699</v>
+      </c>
+      <c r="E801" s="2">
+        <v>499</v>
+      </c>
+      <c r="F801" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G801" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="H801" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I801" s="2"/>
+      <c r="J801" s="2"/>
+      <c r="K801" s="2"/>
+    </row>
+    <row r="802" spans="1:11" ht="15">
+      <c r="A802" s="4">
+        <v>371</v>
+      </c>
+      <c r="B802" s="2" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C802" s="2" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D802" s="2"/>
+      <c r="E802" s="2">
+        <v>355</v>
+      </c>
+      <c r="F802" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G802" s="2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="H802" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I802" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="J802" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K802" s="2"/>
+    </row>
+    <row r="803" spans="1:11" ht="15">
+      <c r="A803" s="4">
+        <v>372</v>
+      </c>
+      <c r="B803" s="2" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C803" s="2" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D803" s="2">
+        <v>589</v>
+      </c>
+      <c r="E803" s="2">
+        <v>358.5</v>
+      </c>
+      <c r="F803" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G803" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H803" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I803" s="2"/>
+      <c r="J803" s="2"/>
+      <c r="K803" s="2"/>
+    </row>
+    <row r="804" spans="1:11" ht="15">
+      <c r="A804" s="4">
+        <v>373</v>
+      </c>
+      <c r="B804" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C804" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D804" s="2">
+        <v>461</v>
+      </c>
+      <c r="E804" s="2">
+        <v>308.02999999999997</v>
+      </c>
+      <c r="F804" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G804" s="2"/>
+      <c r="H804" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I804" s="2"/>
+      <c r="J804" s="2" t="s">
+        <v>1356</v>
+      </c>
+      <c r="K804" s="2">
+        <v>308.02999999999997</v>
+      </c>
+    </row>
+    <row r="805" spans="1:11" ht="30">
+      <c r="A805" s="4">
+        <v>373</v>
+      </c>
+      <c r="B805" s="2" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C805" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D805" s="2">
+        <v>440</v>
+      </c>
+      <c r="E805" s="2">
+        <v>273</v>
+      </c>
+      <c r="F805" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G805" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H805" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I805" s="2"/>
+      <c r="J805" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="K805" s="2">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="806" spans="1:11" ht="30">
+      <c r="A806" s="4">
+        <v>374</v>
+      </c>
+      <c r="B806" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C806" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D806" s="2"/>
+      <c r="E806" s="2">
+        <v>110</v>
+      </c>
+      <c r="F806" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G806" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H806" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I806" s="2"/>
+      <c r="J806" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="K806" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="807" spans="1:11" ht="30">
+      <c r="A807" s="4">
+        <v>374</v>
+      </c>
+      <c r="B807" s="2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C807" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D807" s="2"/>
+      <c r="E807" s="2">
+        <v>91.5</v>
+      </c>
+      <c r="F807" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G807" s="2"/>
+      <c r="H807" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I807" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="J807" s="2"/>
+      <c r="K807" s="2"/>
+    </row>
+    <row r="808" spans="1:11" ht="30">
+      <c r="A808" s="4">
+        <v>375</v>
+      </c>
+      <c r="B808" s="2" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C808" s="2" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D808" s="2">
+        <v>137.6</v>
+      </c>
+      <c r="E808" s="2">
+        <v>95</v>
+      </c>
+      <c r="F808" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G808" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H808" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I808" s="2" t="s">
+        <v>1365</v>
+      </c>
+      <c r="J808" s="2"/>
+      <c r="K808" s="2"/>
+    </row>
+    <row r="809" spans="1:11" ht="30">
+      <c r="A809" s="4">
+        <v>375</v>
+      </c>
+      <c r="B809" s="2" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C809" s="2" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D809" s="2"/>
+      <c r="E809" s="2">
+        <v>119</v>
+      </c>
+      <c r="F809" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G809" s="2"/>
+      <c r="H809" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I809" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="J809" s="2" t="s">
+        <v>1368</v>
+      </c>
+      <c r="K809" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="810" spans="1:11" ht="30">
+      <c r="A810" s="4">
+        <v>375</v>
+      </c>
+      <c r="B810" s="2" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C810" s="2" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D810" s="2">
+        <v>108</v>
+      </c>
+      <c r="E810" s="2">
+        <v>126</v>
+      </c>
+      <c r="F810" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G810" s="2"/>
+      <c r="H810" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I810" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="J810" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="K810" s="2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="811" spans="1:11" ht="30">
+      <c r="A811" s="4">
+        <v>375</v>
+      </c>
+      <c r="B811" s="2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C811" s="2" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D811" s="2"/>
+      <c r="E811" s="2">
+        <v>107</v>
+      </c>
+      <c r="F811" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G811" s="2"/>
+      <c r="H811" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I811" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="J811" s="2" t="s">
+        <v>1374</v>
+      </c>
+      <c r="K811" s="2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="812" spans="1:11" ht="30">
+      <c r="A812" s="4">
+        <v>376</v>
+      </c>
+      <c r="B812" s="2" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C812" s="2" t="s">
+        <v>1376</v>
+      </c>
+      <c r="D812" s="2">
+        <v>650</v>
+      </c>
+      <c r="E812" s="2">
+        <v>426</v>
+      </c>
+      <c r="F812" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G812" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H812" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I812" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="J812" s="2"/>
+      <c r="K812" s="2"/>
+    </row>
+    <row r="813" spans="1:11" ht="30">
+      <c r="A813" s="4">
+        <v>376</v>
+      </c>
+      <c r="B813" s="2" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C813" s="2" t="s">
+        <v>1376</v>
+      </c>
+      <c r="D813" s="2">
+        <v>399</v>
+      </c>
+      <c r="E813" s="2">
+        <v>292.99</v>
+      </c>
+      <c r="F813" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G813" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H813" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I813" s="2"/>
+      <c r="J813" s="2"/>
+      <c r="K813" s="2"/>
+    </row>
+    <row r="814" spans="1:11" ht="30">
+      <c r="A814" s="4">
+        <v>376</v>
+      </c>
+      <c r="B814" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C814" s="2" t="s">
+        <v>1376</v>
+      </c>
+      <c r="D814" s="2">
+        <v>565</v>
+      </c>
+      <c r="E814" s="2">
+        <v>564</v>
+      </c>
+      <c r="F814" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G814" s="2"/>
+      <c r="H814" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I814" s="2"/>
+      <c r="J814" s="2"/>
+      <c r="K814" s="2"/>
+    </row>
+    <row r="815" spans="1:11" ht="30">
+      <c r="A815" s="4">
+        <v>376</v>
+      </c>
+      <c r="B815" s="2" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C815" s="2" t="s">
+        <v>1376</v>
+      </c>
+      <c r="D815" s="2"/>
+      <c r="E815" s="2">
+        <v>576</v>
+      </c>
+      <c r="F815" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G815" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H815" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I815" s="2"/>
+      <c r="J815" s="2"/>
+      <c r="K815" s="2"/>
+    </row>
+    <row r="816" spans="1:11" ht="30">
+      <c r="A816" s="4">
+        <v>377</v>
+      </c>
+      <c r="B816" s="2" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C816" s="2" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D816" s="2"/>
+      <c r="E816" s="2">
+        <v>134</v>
+      </c>
+      <c r="F816" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G816" s="2"/>
+      <c r="H816" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I816" s="2"/>
+      <c r="J816" s="2"/>
+      <c r="K816" s="2"/>
+    </row>
+    <row r="817" spans="1:11" ht="45">
+      <c r="A817" s="4">
+        <v>378</v>
+      </c>
+      <c r="B817" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="C817" s="2" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D817" s="2"/>
+      <c r="E817" s="2">
+        <v>24.57</v>
+      </c>
+      <c r="F817" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G817" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H817" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I817" s="2" t="s">
+        <v>1383</v>
+      </c>
+      <c r="J817" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K817" s="2"/>
+    </row>
+    <row r="818" spans="1:11" ht="30">
+      <c r="A818" s="4">
+        <v>378</v>
+      </c>
+      <c r="B818" s="2" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C818" s="2" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D818" s="2"/>
+      <c r="E818" s="2">
+        <v>218</v>
+      </c>
+      <c r="F818" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G818" s="2"/>
+      <c r="H818" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I818" s="2"/>
+      <c r="J818" s="2"/>
+      <c r="K818" s="2"/>
+    </row>
+    <row r="819" spans="1:11" ht="15">
+      <c r="A819" s="4">
+        <v>378</v>
+      </c>
+      <c r="B819" s="2" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C819" s="2" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D819" s="2"/>
+      <c r="E819" s="2">
+        <v>87</v>
+      </c>
+      <c r="F819" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G819" s="2"/>
+      <c r="H819" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I819" s="2"/>
+      <c r="J819" s="2" t="s">
+        <v>1386</v>
+      </c>
+      <c r="K819" s="2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="820" spans="1:11" ht="30">
+      <c r="A820" s="4">
+        <v>378</v>
+      </c>
+      <c r="B820" s="2" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C820" s="2" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D820" s="2">
+        <v>232</v>
+      </c>
+      <c r="E820" s="2">
+        <v>152</v>
+      </c>
+      <c r="F820" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G820" s="2"/>
+      <c r="H820" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I820" s="2"/>
+      <c r="J820" s="2"/>
+      <c r="K820" s="2"/>
+    </row>
+    <row r="821" spans="1:11" ht="15">
+      <c r="A821" s="4">
+        <v>379</v>
+      </c>
+      <c r="B821" s="2" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C821" s="2" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D821" s="2"/>
+      <c r="E821" s="2">
+        <v>245</v>
+      </c>
+      <c r="F821" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G821" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H821" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I821" s="2"/>
+      <c r="J821" s="2" t="s">
+        <v>1389</v>
+      </c>
+      <c r="K821" s="2">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="822" spans="1:11" ht="30">
+      <c r="A822" s="4">
+        <v>380</v>
+      </c>
+      <c r="B822" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="C822" s="2" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D822" s="2">
+        <v>195</v>
+      </c>
+      <c r="E822" s="2">
+        <v>119</v>
+      </c>
+      <c r="F822" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G822" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="H822" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I822" s="2"/>
+      <c r="J822" s="2"/>
+      <c r="K822" s="2"/>
+    </row>
+    <row r="823" spans="1:11" ht="15">
+      <c r="A823" s="4">
+        <v>381</v>
+      </c>
+      <c r="B823" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="C823" s="2" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D823" s="2">
+        <v>158</v>
+      </c>
+      <c r="E823" s="2">
+        <v>98.9</v>
+      </c>
+      <c r="F823" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G823" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H823" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I823" s="2"/>
+      <c r="J823" s="2"/>
+      <c r="K823" s="2"/>
+    </row>
+    <row r="824" spans="1:11" ht="30">
+      <c r="A824" s="4">
+        <v>381</v>
+      </c>
+      <c r="B824" s="2" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C824" s="2" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D824" s="2">
+        <v>300</v>
+      </c>
+      <c r="E824" s="2">
+        <v>183</v>
+      </c>
+      <c r="F824" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G824" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H824" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I824" s="2"/>
+      <c r="J824" s="2"/>
+      <c r="K824" s="2"/>
+    </row>
+    <row r="825" spans="1:11" ht="30">
+      <c r="A825" s="4">
+        <v>382</v>
+      </c>
+      <c r="B825" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C825" s="2" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D825" s="2"/>
+      <c r="E825" s="2">
+        <v>149</v>
+      </c>
+      <c r="F825" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G825" s="2" t="s">
+        <v>1395</v>
+      </c>
+      <c r="H825" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I825" s="2"/>
+      <c r="J825" s="2" t="s">
+        <v>1396</v>
+      </c>
+      <c r="K825" s="2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="826" spans="1:11" ht="30">
+      <c r="A826" s="4">
+        <v>382</v>
+      </c>
+      <c r="B826" s="2" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C826" s="2" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D826" s="2"/>
+      <c r="E826" s="2">
+        <v>168</v>
+      </c>
+      <c r="F826" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G826" s="2" t="s">
+        <v>1398</v>
+      </c>
+      <c r="H826" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I826" s="2"/>
+      <c r="J826" s="2" t="s">
+        <v>1399</v>
+      </c>
+      <c r="K826" s="2">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="827" spans="1:11" ht="30">
+      <c r="A827" s="4">
+        <v>383</v>
+      </c>
+      <c r="B827" s="2" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C827" s="2" t="s">
+        <v>1401</v>
+      </c>
+      <c r="D827" s="2">
+        <v>258</v>
+      </c>
+      <c r="E827" s="2">
+        <v>138</v>
+      </c>
+      <c r="F827" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G827" s="2"/>
+      <c r="H827" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I827" s="2"/>
+      <c r="J827" s="2"/>
+      <c r="K827" s="2"/>
+    </row>
+    <row r="828" spans="1:11" ht="30">
+      <c r="A828" s="4">
+        <v>384</v>
+      </c>
+      <c r="B828" s="2" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C828" s="2" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D828" s="2">
+        <v>193.4</v>
+      </c>
+      <c r="E828" s="2">
+        <v>118</v>
+      </c>
+      <c r="F828" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G828" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H828" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I828" s="2"/>
+      <c r="J828" s="2"/>
+      <c r="K828" s="2"/>
+    </row>
+    <row r="829" spans="1:11" ht="30">
+      <c r="A829" s="4">
+        <v>385</v>
+      </c>
+      <c r="B829" s="2" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C829" s="2" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D829" s="2"/>
+      <c r="E829" s="2">
+        <v>293</v>
+      </c>
+      <c r="F829" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G829" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="H829" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I829" s="2"/>
+      <c r="J829" s="2"/>
+      <c r="K829" s="2"/>
+    </row>
+    <row r="830" spans="1:11" ht="30">
+      <c r="A830" s="4">
+        <v>386</v>
+      </c>
+      <c r="B830" s="2" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C830" s="2" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D830" s="2">
+        <v>399</v>
+      </c>
+      <c r="E830" s="2">
+        <v>224</v>
+      </c>
+      <c r="F830" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G830" s="2"/>
+      <c r="H830" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I830" s="2"/>
+      <c r="J830" s="2"/>
+      <c r="K830" s="2"/>
+    </row>
+    <row r="831" spans="1:11" ht="30">
+      <c r="A831" s="4">
+        <v>386</v>
+      </c>
+      <c r="B831" s="2" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C831" s="2" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D831" s="2"/>
+      <c r="E831" s="2">
+        <v>249</v>
+      </c>
+      <c r="F831" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G831" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="H831" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I831" s="2"/>
+      <c r="J831" s="2"/>
+      <c r="K831" s="2"/>
+    </row>
+    <row r="832" spans="1:11" ht="30">
+      <c r="A832" s="4">
+        <v>386</v>
+      </c>
+      <c r="B832" s="2" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C832" s="2" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D832" s="2"/>
+      <c r="E832" s="2">
+        <v>212</v>
+      </c>
+      <c r="F832" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G832" s="2"/>
+      <c r="H832" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I832" s="2"/>
+      <c r="J832" s="2" t="s">
+        <v>1410</v>
+      </c>
+      <c r="K832" s="2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="833" spans="1:11" ht="30">
+      <c r="A833" s="4">
+        <v>387</v>
+      </c>
+      <c r="B833" s="2" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C833" s="2" t="s">
+        <v>1411</v>
+      </c>
+      <c r="D833" s="2">
+        <v>399</v>
+      </c>
+      <c r="E833" s="2">
+        <v>224</v>
+      </c>
+      <c r="F833" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G833" s="2"/>
+      <c r="H833" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I833" s="2"/>
+      <c r="J833" s="2" t="s">
+        <v>1412</v>
+      </c>
+      <c r="K833" s="2">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="834" spans="1:11" ht="30">
+      <c r="A834" s="4">
+        <v>388</v>
+      </c>
+      <c r="B834" s="2" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C834" s="2" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D834" s="2"/>
+      <c r="E834" s="2">
+        <v>112</v>
+      </c>
+      <c r="F834" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G834" s="2"/>
+      <c r="H834" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I834" s="2"/>
+      <c r="J834" s="2" t="s">
+        <v>1415</v>
+      </c>
+      <c r="K834" s="2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="835" spans="1:11" ht="30">
+      <c r="A835" s="4">
+        <v>389</v>
+      </c>
+      <c r="B835" s="2" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C835" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="D835" s="2">
+        <v>96</v>
+      </c>
+      <c r="E835" s="2">
+        <v>86</v>
+      </c>
+      <c r="F835" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G835" s="2" t="s">
+        <v>1418</v>
+      </c>
+      <c r="H835" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I835" s="2"/>
+      <c r="J835" s="2"/>
+      <c r="K835" s="2"/>
+    </row>
+    <row r="836" spans="1:11" ht="30">
+      <c r="A836" s="4">
+        <v>390</v>
+      </c>
+      <c r="B836" s="2" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C836" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D836" s="2">
+        <v>68.900000000000006</v>
+      </c>
+      <c r="E836" s="2">
+        <v>68.900000000000006</v>
+      </c>
+      <c r="F836" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G836" s="2" t="s">
+        <v>1421</v>
+      </c>
+      <c r="H836" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I836" s="2"/>
+      <c r="J836" s="2" t="s">
+        <v>1422</v>
+      </c>
+      <c r="K836" s="2">
+        <v>68.900000000000006</v>
+      </c>
+    </row>
+    <row r="837" spans="1:11" ht="30">
+      <c r="A837" s="4">
+        <v>391</v>
+      </c>
+      <c r="B837" s="2" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C837" s="2" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D837" s="2"/>
+      <c r="E837" s="2">
+        <v>309</v>
+      </c>
+      <c r="F837" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G837" s="2"/>
+      <c r="H837" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I837" s="2"/>
+      <c r="J837" s="2"/>
+      <c r="K837" s="2"/>
+    </row>
+    <row r="838" spans="1:11" ht="30">
+      <c r="A838" s="4">
+        <v>391</v>
+      </c>
+      <c r="B838" s="2" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C838" s="2" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D838" s="2">
+        <v>359</v>
+      </c>
+      <c r="E838" s="2">
+        <v>286</v>
+      </c>
+      <c r="F838" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G838" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H838" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I838" s="2"/>
+      <c r="J838" s="2" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K838" s="2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="839" spans="1:11" ht="30">
+      <c r="A839" s="4">
+        <v>392</v>
+      </c>
+      <c r="B839" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C839" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D839" s="2"/>
+      <c r="E839" s="2">
+        <v>299</v>
+      </c>
+      <c r="F839" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G839" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H839" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I839" s="2"/>
+      <c r="J839" s="2"/>
+      <c r="K839" s="2"/>
+    </row>
+    <row r="840" spans="1:11" ht="30">
+      <c r="A840" s="4">
+        <v>392</v>
+      </c>
+      <c r="B840" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C840" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D840" s="2"/>
+      <c r="E840" s="2">
+        <v>169</v>
+      </c>
+      <c r="F840" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G840" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="H840" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I840" s="2"/>
+      <c r="J840" s="2"/>
+      <c r="K840" s="2"/>
+    </row>
+    <row r="841" spans="1:11" ht="30">
+      <c r="A841" s="4">
+        <v>392</v>
+      </c>
+      <c r="B841" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C841" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D841" s="2"/>
+      <c r="E841" s="2">
+        <v>169</v>
+      </c>
+      <c r="F841" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G841" s="2" t="s">
+        <v>1430</v>
+      </c>
+      <c r="H841" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I841" s="2"/>
+      <c r="J841" s="2"/>
+      <c r="K841" s="2"/>
+    </row>
+    <row r="842" spans="1:11" ht="30">
+      <c r="A842" s="4">
+        <v>393</v>
+      </c>
+      <c r="B842" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="C842" s="2" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D842" s="2"/>
+      <c r="E842" s="2">
+        <v>119.9</v>
+      </c>
+      <c r="F842" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G842" s="2"/>
+      <c r="H842" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I842" s="2"/>
+      <c r="J842" s="2" t="s">
+        <v>1433</v>
+      </c>
+      <c r="K842" s="2">
+        <v>119.9</v>
+      </c>
+    </row>
+    <row r="843" spans="1:11" ht="15">
+      <c r="A843" s="4">
+        <v>394</v>
+      </c>
+      <c r="B843" s="2" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C843" s="2" t="s">
+        <v>1435</v>
+      </c>
+      <c r="D843" s="2">
+        <v>599</v>
+      </c>
+      <c r="E843" s="2">
+        <v>368</v>
+      </c>
+      <c r="F843" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G843" s="2"/>
+      <c r="H843" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I843" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="J843" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K843" s="2"/>
+    </row>
+    <row r="844" spans="1:11" ht="30">
+      <c r="A844" s="4">
+        <v>395</v>
+      </c>
+      <c r="B844" s="2" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C844" s="2" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D844" s="2">
+        <v>1099</v>
+      </c>
+      <c r="E844" s="2">
+        <v>736.36</v>
+      </c>
+      <c r="F844" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G844" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H844" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I844" s="2"/>
+      <c r="J844" s="2"/>
+      <c r="K844" s="2"/>
+    </row>
+    <row r="845" spans="1:11" ht="30">
+      <c r="A845" s="4">
+        <v>396</v>
+      </c>
+      <c r="B845" s="2" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C845" s="2" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D845" s="2">
+        <v>845</v>
+      </c>
+      <c r="E845" s="2">
+        <v>549.49</v>
+      </c>
+      <c r="F845" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G845" s="2" t="s">
+        <v>1440</v>
+      </c>
+      <c r="H845" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I845" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="J845" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K845" s="2"/>
+    </row>
+    <row r="846" spans="1:11" ht="30">
+      <c r="A846" s="4">
+        <v>396</v>
+      </c>
+      <c r="B846" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C846" s="2" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D846" s="2">
+        <v>1099</v>
+      </c>
+      <c r="E846" s="2">
+        <v>736.36</v>
+      </c>
+      <c r="F846" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G846" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H846" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I846" s="2"/>
+      <c r="J846" s="2"/>
+      <c r="K846" s="2"/>
+    </row>
+    <row r="847" spans="1:11" ht="30">
+      <c r="A847" s="4">
+        <v>397</v>
+      </c>
+      <c r="B847" s="2" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C847" s="2" t="s">
+        <v>1443</v>
+      </c>
+      <c r="D847" s="2"/>
+      <c r="E847" s="2">
+        <v>585</v>
+      </c>
+      <c r="F847" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G847" s="2"/>
+      <c r="H847" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I847" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="J847" s="2" t="s">
+        <v>1444</v>
+      </c>
+      <c r="K847" s="2">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="848" spans="1:11" ht="30">
+      <c r="A848" s="4">
+        <v>398</v>
+      </c>
+      <c r="B848" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C848" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D848" s="2"/>
+      <c r="E848" s="2">
+        <v>154.69999999999999</v>
+      </c>
+      <c r="F848" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G848" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H848" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I848" s="2"/>
+      <c r="J848" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="K848" s="2">
+        <v>154.69999999999999</v>
+      </c>
+    </row>
+    <row r="849" spans="1:11" ht="30">
+      <c r="A849" s="4">
+        <v>399</v>
+      </c>
+      <c r="B849" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C849" s="2" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D849" s="2"/>
+      <c r="E849" s="2">
+        <v>899</v>
+      </c>
+      <c r="F849" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G849" s="2" t="s">
+        <v>1449</v>
+      </c>
+      <c r="H849" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I849" s="2"/>
+      <c r="J849" s="2" t="s">
+        <v>1450</v>
+      </c>
+      <c r="K849" s="2">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="850" spans="1:11" ht="30">
+      <c r="A850" s="4">
+        <v>399</v>
+      </c>
+      <c r="B850" s="2" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C850" s="2" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D850" s="2">
+        <v>6991</v>
+      </c>
+      <c r="E850" s="2">
+        <v>699</v>
+      </c>
+      <c r="F850" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G850" s="2" t="s">
+        <v>1452</v>
+      </c>
+      <c r="H850" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I850" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="J850" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K850" s="2"/>
+    </row>
+    <row r="851" spans="1:11" ht="30">
+      <c r="A851" s="4">
+        <v>399</v>
+      </c>
+      <c r="B851" s="2" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C851" s="2" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D851" s="2"/>
+      <c r="E851" s="2">
+        <v>1026</v>
+      </c>
+      <c r="F851" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G851" s="2"/>
+      <c r="H851" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I851" s="2"/>
+      <c r="J851" s="2" t="s">
+        <v>1454</v>
+      </c>
+      <c r="K851" s="2">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="852" spans="1:11" ht="30">
+      <c r="A852" s="4">
+        <v>400</v>
+      </c>
+      <c r="B852" s="2" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C852" s="2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D852" s="2">
+        <v>380</v>
+      </c>
+      <c r="E852" s="2">
+        <v>304</v>
+      </c>
+      <c r="F852" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G852" s="2" t="s">
+        <v>1457</v>
+      </c>
+      <c r="H852" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I852" s="2"/>
+      <c r="J852" s="2" t="s">
+        <v>1454</v>
+      </c>
+      <c r="K852" s="2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="853" spans="1:11" ht="30">
+      <c r="A853" s="4">
+        <v>400</v>
+      </c>
+      <c r="B853" s="2" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C853" s="2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D853" s="2">
+        <v>380</v>
+      </c>
+      <c r="E853" s="2">
+        <v>38</v>
+      </c>
+      <c r="F853" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G853" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H853" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I853" s="2"/>
+      <c r="J853" s="2"/>
+      <c r="K853" s="2"/>
+    </row>
+    <row r="854" spans="1:11" ht="30">
+      <c r="A854" s="4">
+        <v>377</v>
+      </c>
+      <c r="B854" s="2" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C854" s="2" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D854" s="2"/>
+      <c r="E854" s="2" t="s">
+        <v>1460</v>
+      </c>
+      <c r="F854" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G854" s="2"/>
+      <c r="H854" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I854" s="2"/>
+      <c r="J854" s="2"/>
+      <c r="K854" s="2"/>
+    </row>
+    <row r="855" spans="1:11" ht="45">
+      <c r="A855" s="4">
+        <v>378</v>
+      </c>
+      <c r="B855" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="C855" s="2" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D855" s="2"/>
+      <c r="E855" s="2" t="s">
+        <v>1461</v>
+      </c>
+      <c r="F855" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G855" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H855" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I855" s="2" t="s">
+        <v>1383</v>
+      </c>
+      <c r="J855" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K855" s="2"/>
+    </row>
+    <row r="856" spans="1:11" ht="30">
+      <c r="A856" s="4">
+        <v>378</v>
+      </c>
+      <c r="B856" s="2" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C856" s="2" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D856" s="2"/>
+      <c r="E856" s="2" t="s">
+        <v>1462</v>
+      </c>
+      <c r="F856" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G856" s="2"/>
+      <c r="H856" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I856" s="2"/>
+      <c r="J856" s="2"/>
+      <c r="K856" s="2"/>
+    </row>
+    <row r="857" spans="1:11" ht="15">
+      <c r="A857" s="4">
+        <v>378</v>
+      </c>
+      <c r="B857" s="2" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C857" s="2" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D857" s="2"/>
+      <c r="E857" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="F857" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G857" s="2"/>
+      <c r="H857" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I857" s="2"/>
+      <c r="J857" s="2" t="s">
+        <v>1386</v>
+      </c>
+      <c r="K857" s="2" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="858" spans="1:11" ht="30">
+      <c r="A858" s="4">
+        <v>378</v>
+      </c>
+      <c r="B858" s="2" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C858" s="2" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D858" s="2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="E858" s="2" t="s">
+        <v>1465</v>
+      </c>
+      <c r="F858" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G858" s="2"/>
+      <c r="H858" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I858" s="2"/>
+      <c r="J858" s="2"/>
+      <c r="K858" s="2"/>
+    </row>
+    <row r="859" spans="1:11" ht="15">
+      <c r="A859" s="4">
+        <v>379</v>
+      </c>
+      <c r="B859" s="2" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C859" s="2" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D859" s="2"/>
+      <c r="E859" s="2" t="s">
+        <v>1466</v>
+      </c>
+      <c r="F859" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G859" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H859" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I859" s="2"/>
+      <c r="J859" s="2" t="s">
+        <v>1389</v>
+      </c>
+      <c r="K859" s="2" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="860" spans="1:11" ht="30">
+      <c r="A860" s="4">
+        <v>380</v>
+      </c>
+      <c r="B860" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="C860" s="2" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D860" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="E860" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F860" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G860" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="H860" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I860" s="2"/>
+      <c r="J860" s="2"/>
+      <c r="K860" s="2"/>
+    </row>
+    <row r="861" spans="1:11" ht="15">
+      <c r="A861" s="4">
+        <v>381</v>
+      </c>
+      <c r="B861" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="C861" s="2" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D861" s="2" t="s">
+        <v>1469</v>
+      </c>
+      <c r="E861" s="2" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F861" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G861" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H861" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I861" s="2"/>
+      <c r="J861" s="2"/>
+      <c r="K861" s="2"/>
+    </row>
+    <row r="862" spans="1:11" ht="30">
+      <c r="A862" s="4">
+        <v>381</v>
+      </c>
+      <c r="B862" s="2" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C862" s="2" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D862" s="2" t="s">
+        <v>1471</v>
+      </c>
+      <c r="E862" s="2" t="s">
+        <v>1472</v>
+      </c>
+      <c r="F862" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G862" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H862" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I862" s="2"/>
+      <c r="J862" s="2"/>
+      <c r="K862" s="2"/>
+    </row>
+    <row r="863" spans="1:11" ht="30">
+      <c r="A863" s="4">
+        <v>382</v>
+      </c>
+      <c r="B863" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C863" s="2" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D863" s="2"/>
+      <c r="E863" s="2" t="s">
+        <v>1473</v>
+      </c>
+      <c r="F863" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G863" s="2" t="s">
+        <v>1395</v>
+      </c>
+      <c r="H863" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I863" s="2"/>
+      <c r="J863" s="2" t="s">
+        <v>1396</v>
+      </c>
+      <c r="K863" s="2" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="864" spans="1:11" ht="30">
+      <c r="A864" s="4">
+        <v>382</v>
+      </c>
+      <c r="B864" s="2" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C864" s="2" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D864" s="2"/>
+      <c r="E864" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F864" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G864" s="2" t="s">
+        <v>1398</v>
+      </c>
+      <c r="H864" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I864" s="2"/>
+      <c r="J864" s="2" t="s">
+        <v>1399</v>
+      </c>
+      <c r="K864" s="2" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="865" spans="1:11" ht="30">
+      <c r="A865" s="4">
+        <v>383</v>
+      </c>
+      <c r="B865" s="2" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C865" s="2" t="s">
+        <v>1401</v>
+      </c>
+      <c r="D865" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E865" s="2" t="s">
+        <v>1476</v>
+      </c>
+      <c r="F865" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G865" s="2"/>
+      <c r="H865" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I865" s="2"/>
+      <c r="J865" s="2"/>
+      <c r="K865" s="2"/>
+    </row>
+    <row r="866" spans="1:11" ht="30">
+      <c r="A866" s="4">
+        <v>384</v>
+      </c>
+      <c r="B866" s="2" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C866" s="2" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D866" s="2" t="s">
+        <v>1477</v>
+      </c>
+      <c r="E866" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F866" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G866" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H866" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I866" s="2"/>
+      <c r="J866" s="2"/>
+      <c r="K866" s="2"/>
+    </row>
+    <row r="867" spans="1:11" ht="30">
+      <c r="A867" s="4">
+        <v>385</v>
+      </c>
+      <c r="B867" s="2" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C867" s="2" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D867" s="2"/>
+      <c r="E867" s="2" t="s">
+        <v>1479</v>
+      </c>
+      <c r="F867" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G867" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="H867" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I867" s="2"/>
+      <c r="J867" s="2"/>
+      <c r="K867" s="2"/>
+    </row>
+    <row r="868" spans="1:11" ht="30">
+      <c r="A868" s="4">
+        <v>386</v>
+      </c>
+      <c r="B868" s="2" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C868" s="2" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D868" s="2" t="s">
+        <v>1480</v>
+      </c>
+      <c r="E868" s="2" t="s">
+        <v>1481</v>
+      </c>
+      <c r="F868" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G868" s="2"/>
+      <c r="H868" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I868" s="2"/>
+      <c r="J868" s="2"/>
+      <c r="K868" s="2"/>
+    </row>
+    <row r="869" spans="1:11" ht="30">
+      <c r="A869" s="4">
+        <v>386</v>
+      </c>
+      <c r="B869" s="2" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C869" s="2" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D869" s="2"/>
+      <c r="E869" s="2" t="s">
+        <v>1482</v>
+      </c>
+      <c r="F869" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G869" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="H869" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I869" s="2"/>
+      <c r="J869" s="2"/>
+      <c r="K869" s="2"/>
+    </row>
+    <row r="870" spans="1:11" ht="30">
+      <c r="A870" s="4">
+        <v>386</v>
+      </c>
+      <c r="B870" s="2" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C870" s="2" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D870" s="2"/>
+      <c r="E870" s="2" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F870" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G870" s="2"/>
+      <c r="H870" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I870" s="2"/>
+      <c r="J870" s="2" t="s">
+        <v>1410</v>
+      </c>
+      <c r="K870" s="2" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="871" spans="1:11" ht="30">
+      <c r="A871" s="4">
+        <v>387</v>
+      </c>
+      <c r="B871" s="2" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C871" s="2" t="s">
+        <v>1411</v>
+      </c>
+      <c r="D871" s="2" t="s">
+        <v>1480</v>
+      </c>
+      <c r="E871" s="2" t="s">
+        <v>1484</v>
+      </c>
+      <c r="F871" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G871" s="2"/>
+      <c r="H871" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I871" s="2"/>
+      <c r="J871" s="2" t="s">
+        <v>1412</v>
+      </c>
+      <c r="K871" s="2" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="872" spans="1:11" ht="30">
+      <c r="A872" s="4">
+        <v>388</v>
+      </c>
+      <c r="B872" s="2" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C872" s="2" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D872" s="2"/>
+      <c r="E872" s="2" t="s">
+        <v>1485</v>
+      </c>
+      <c r="F872" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G872" s="2"/>
+      <c r="H872" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I872" s="2"/>
+      <c r="J872" s="2" t="s">
+        <v>1415</v>
+      </c>
+      <c r="K872" s="2" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="873" spans="1:11" ht="30">
+      <c r="A873" s="4">
+        <v>389</v>
+      </c>
+      <c r="B873" s="2" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C873" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="D873" s="2" t="s">
+        <v>1486</v>
+      </c>
+      <c r="E873" s="2" t="s">
+        <v>1487</v>
+      </c>
+      <c r="F873" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G873" s="2" t="s">
+        <v>1418</v>
+      </c>
+      <c r="H873" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I873" s="2"/>
+      <c r="J873" s="2"/>
+      <c r="K873" s="2"/>
+    </row>
+    <row r="874" spans="1:11" ht="30">
+      <c r="A874" s="4">
+        <v>390</v>
+      </c>
+      <c r="B874" s="2" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C874" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D874" s="2" t="s">
+        <v>1488</v>
+      </c>
+      <c r="E874" s="2" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F874" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G874" s="2" t="s">
+        <v>1421</v>
+      </c>
+      <c r="H874" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I874" s="2"/>
+      <c r="J874" s="2" t="s">
+        <v>1422</v>
+      </c>
+      <c r="K874" s="2" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="875" spans="1:11" ht="30">
+      <c r="A875" s="4">
+        <v>391</v>
+      </c>
+      <c r="B875" s="2" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C875" s="2" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D875" s="2"/>
+      <c r="E875" s="2" t="s">
+        <v>1489</v>
+      </c>
+      <c r="F875" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G875" s="2"/>
+      <c r="H875" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I875" s="2"/>
+      <c r="J875" s="2"/>
+      <c r="K875" s="2"/>
+    </row>
+    <row r="876" spans="1:11" ht="30">
+      <c r="A876" s="4">
+        <v>391</v>
+      </c>
+      <c r="B876" s="2" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C876" s="2" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D876" s="2" t="s">
+        <v>1490</v>
+      </c>
+      <c r="E876" s="2" t="s">
+        <v>1491</v>
+      </c>
+      <c r="F876" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G876" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H876" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I876" s="2"/>
+      <c r="J876" s="2" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K876" s="2" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="877" spans="1:11" ht="30">
+      <c r="A877" s="4">
+        <v>392</v>
+      </c>
+      <c r="B877" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C877" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D877" s="2"/>
+      <c r="E877" s="2" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F877" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G877" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H877" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I877" s="2"/>
+      <c r="J877" s="2"/>
+      <c r="K877" s="2"/>
+    </row>
+    <row r="878" spans="1:11" ht="30">
+      <c r="A878" s="4">
+        <v>392</v>
+      </c>
+      <c r="B878" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C878" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D878" s="2"/>
+      <c r="E878" s="2" t="s">
+        <v>1493</v>
+      </c>
+      <c r="F878" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G878" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="H878" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I878" s="2"/>
+      <c r="J878" s="2"/>
+      <c r="K878" s="2"/>
+    </row>
+    <row r="879" spans="1:11" ht="30">
+      <c r="A879" s="4">
+        <v>392</v>
+      </c>
+      <c r="B879" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C879" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D879" s="2"/>
+      <c r="E879" s="2" t="s">
+        <v>1493</v>
+      </c>
+      <c r="F879" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G879" s="2" t="s">
+        <v>1430</v>
+      </c>
+      <c r="H879" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I879" s="2"/>
+      <c r="J879" s="2"/>
+      <c r="K879" s="2"/>
+    </row>
+    <row r="880" spans="1:11" ht="30">
+      <c r="A880" s="4">
+        <v>393</v>
+      </c>
+      <c r="B880" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="C880" s="2" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D880" s="2"/>
+      <c r="E880" s="2" t="s">
+        <v>1494</v>
+      </c>
+      <c r="F880" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G880" s="2"/>
+      <c r="H880" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I880" s="2"/>
+      <c r="J880" s="2" t="s">
+        <v>1433</v>
+      </c>
+      <c r="K880" s="2" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="881" spans="1:11" ht="15">
+      <c r="A881" s="4">
+        <v>394</v>
+      </c>
+      <c r="B881" s="2" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C881" s="2" t="s">
+        <v>1435</v>
+      </c>
+      <c r="D881" s="2" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E881" s="2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="F881" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G881" s="2"/>
+      <c r="H881" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I881" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="J881" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K881" s="2"/>
+    </row>
+    <row r="882" spans="1:11" ht="45">
+      <c r="A882" s="4">
+        <v>394</v>
+      </c>
+      <c r="B882" s="2" t="s">
+        <v>1497</v>
+      </c>
+      <c r="C882" s="2" t="s">
+        <v>1435</v>
+      </c>
+      <c r="D882" s="2"/>
+      <c r="E882" s="2"/>
+      <c r="F882" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G882" s="2"/>
+      <c r="H882" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I882" s="2" t="s">
+        <v>1383</v>
+      </c>
+      <c r="J882" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K882" s="2"/>
+    </row>
+    <row r="883" spans="1:11" ht="30">
+      <c r="A883" s="4">
+        <v>394</v>
+      </c>
+      <c r="B883" s="2" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C883" s="2" t="s">
+        <v>1435</v>
+      </c>
+      <c r="D883" s="2"/>
+      <c r="E883" s="2"/>
+      <c r="F883" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G883" s="2"/>
+      <c r="H883" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I883" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="J883" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K883" s="2"/>
+    </row>
+    <row r="884" spans="1:11" ht="30">
+      <c r="A884" s="4">
+        <v>394</v>
+      </c>
+      <c r="B884" s="2" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C884" s="2" t="s">
+        <v>1435</v>
+      </c>
+      <c r="D884" s="2"/>
+      <c r="E884" s="2"/>
+      <c r="F884" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G884" s="2"/>
+      <c r="H884" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I884" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="J884" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K884" s="2"/>
+    </row>
+    <row r="885" spans="1:11" ht="30">
+      <c r="A885" s="4">
+        <v>395</v>
+      </c>
+      <c r="B885" s="2" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C885" s="2" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D885" s="2" t="s">
+        <v>1500</v>
+      </c>
+      <c r="E885" s="2" t="s">
+        <v>1501</v>
+      </c>
+      <c r="F885" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G885" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H885" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I885" s="2"/>
+      <c r="J885" s="2"/>
+      <c r="K885" s="2"/>
+    </row>
+    <row r="886" spans="1:11" ht="45">
+      <c r="A886" s="4">
+        <v>395</v>
+      </c>
+      <c r="B886" s="2" t="s">
+        <v>1497</v>
+      </c>
+      <c r="C886" s="2" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D886" s="2"/>
+      <c r="E886" s="2"/>
+      <c r="F886" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G886" s="2"/>
+      <c r="H886" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I886" s="2" t="s">
+        <v>1383</v>
+      </c>
+      <c r="J886" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K886" s="2"/>
+    </row>
+    <row r="887" spans="1:11" ht="30">
+      <c r="A887" s="4">
+        <v>396</v>
+      </c>
+      <c r="B887" s="2" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C887" s="2" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D887" s="2" t="s">
+        <v>1502</v>
+      </c>
+      <c r="E887" s="2" t="s">
+        <v>1503</v>
+      </c>
+      <c r="F887" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G887" s="2" t="s">
+        <v>1440</v>
+      </c>
+      <c r="H887" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I887" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="J887" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K887" s="2"/>
+    </row>
+    <row r="888" spans="1:11" ht="30">
+      <c r="A888" s="4">
+        <v>396</v>
+      </c>
+      <c r="B888" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C888" s="2" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D888" s="2" t="s">
+        <v>1500</v>
+      </c>
+      <c r="E888" s="2" t="s">
+        <v>1501</v>
+      </c>
+      <c r="F888" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G888" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H888" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I888" s="2"/>
+      <c r="J888" s="2"/>
+      <c r="K888" s="2"/>
+    </row>
+    <row r="889" spans="1:11" ht="30">
+      <c r="A889" s="4">
+        <v>397</v>
+      </c>
+      <c r="B889" s="2" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C889" s="2" t="s">
+        <v>1443</v>
+      </c>
+      <c r="D889" s="2"/>
+      <c r="E889" s="2" t="s">
+        <v>1504</v>
+      </c>
+      <c r="F889" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G889" s="2"/>
+      <c r="H889" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I889" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="J889" s="2" t="s">
+        <v>1444</v>
+      </c>
+      <c r="K889" s="2" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="890" spans="1:11" ht="30">
+      <c r="A890" s="4">
+        <v>398</v>
+      </c>
+      <c r="B890" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C890" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D890" s="2"/>
+      <c r="E890" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="F890" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G890" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H890" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I890" s="2"/>
+      <c r="J890" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="K890" s="2" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="891" spans="1:11" ht="45">
+      <c r="A891" s="4">
+        <v>399</v>
+      </c>
+      <c r="B891" s="2" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C891" s="2" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D891" s="2"/>
+      <c r="E891" s="2"/>
+      <c r="F891" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G891" s="2"/>
+      <c r="H891" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I891" s="2" t="s">
+        <v>1383</v>
+      </c>
+      <c r="J891" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K891" s="2"/>
+    </row>
+    <row r="892" spans="1:11" ht="30">
+      <c r="A892" s="4">
+        <v>399</v>
+      </c>
+      <c r="B892" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C892" s="2" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D892" s="2"/>
+      <c r="E892" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F892" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G892" s="2" t="s">
+        <v>1449</v>
+      </c>
+      <c r="H892" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I892" s="2"/>
+      <c r="J892" s="2" t="s">
+        <v>1450</v>
+      </c>
+      <c r="K892" s="2" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="893" spans="1:11" ht="30">
+      <c r="A893" s="4">
+        <v>399</v>
+      </c>
+      <c r="B893" s="2" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C893" s="2" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D893" s="2" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E893" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F893" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G893" s="2" t="s">
+        <v>1452</v>
+      </c>
+      <c r="H893" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I893" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="J893" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K893" s="2"/>
+    </row>
+    <row r="894" spans="1:11" ht="30">
+      <c r="A894" s="4">
+        <v>399</v>
+      </c>
+      <c r="B894" s="2" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C894" s="2" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D894" s="2"/>
+      <c r="E894" s="2" t="s">
+        <v>1510</v>
+      </c>
+      <c r="F894" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G894" s="2"/>
+      <c r="H894" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I894" s="2"/>
+      <c r="J894" s="2" t="s">
+        <v>1454</v>
+      </c>
+      <c r="K894" s="2" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="895" spans="1:11" ht="30">
+      <c r="A895" s="4">
+        <v>400</v>
+      </c>
+      <c r="B895" s="2" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C895" s="2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D895" s="2" t="s">
+        <v>1511</v>
+      </c>
+      <c r="E895" s="2" t="s">
+        <v>1512</v>
+      </c>
+      <c r="F895" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G895" s="2" t="s">
+        <v>1457</v>
+      </c>
+      <c r="H895" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I895" s="2"/>
+      <c r="J895" s="2" t="s">
+        <v>1454</v>
+      </c>
+      <c r="K895" s="2" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="896" spans="1:11" ht="30">
+      <c r="A896" s="4">
+        <v>400</v>
+      </c>
+      <c r="B896" s="2" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C896" s="2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D896" s="2" t="s">
+        <v>1511</v>
+      </c>
+      <c r="E896" s="2" t="s">
+        <v>1513</v>
+      </c>
+      <c r="F896" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G896" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H896" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I896" s="2"/>
+      <c r="J896" s="2"/>
+      <c r="K896" s="2"/>
+    </row>
+    <row r="897" spans="1:11" ht="30">
+      <c r="A897" s="4">
+        <v>401</v>
+      </c>
+      <c r="B897" s="2" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C897" s="2" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D897" s="2" t="s">
+        <v>1516</v>
+      </c>
+      <c r="E897" s="2" t="s">
+        <v>1517</v>
+      </c>
+      <c r="F897" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G897" s="2"/>
+      <c r="H897" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I897" s="2"/>
+      <c r="J897" s="2" t="s">
+        <v>1518</v>
+      </c>
+      <c r="K897" s="2" t="s">
+        <v>1517</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
